--- a/assets/translations/Spanish.Spain.es-ES.xlsx
+++ b/assets/translations/Spanish.Spain.es-ES.xlsx
@@ -1,14 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/translations/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E3CF1D-EAB5-0A44-A3AA-00C20B235501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="5180" yWindow="620" windowWidth="51200" windowHeight="28180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Contributors" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Statements" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Key messages" sheetId="3" r:id="rId6"/>
+    <sheet name="Contributors" sheetId="1" r:id="rId1"/>
+    <sheet name="Statements" sheetId="2" r:id="rId2"/>
+    <sheet name="Key messages" sheetId="3" r:id="rId3"/>
+    <sheet name="Misc" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="/FUNB2oG1IwLD4uOvZd8mpcmp5xPGcvWmRSjqNUBr+w="/>
@@ -18,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="222">
   <si>
     <t>Last name</t>
   </si>
@@ -49,10 +59,10 @@
   <si>
     <r>
       <rPr>
+        <u/>
+        <sz val="12"/>
+        <color rgb="FF70AD46"/>
         <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF70AD46"/>
-        <sz val="12.0"/>
-        <u/>
       </rPr>
       <t>isabellafamu@gmail.com</t>
     </r>
@@ -237,25 +247,28 @@
   <si>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD47"/>
         <rFont val="Calibri"/>
-        <color rgb="FF70AD47"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">El color, la intensidad y el patrón de la luz diurna cambia a lo largo del día, con las estaciones </t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF741B47"/>
         <rFont val="Calibri"/>
-        <color rgb="FF741B47"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t>del año</t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD47"/>
         <rFont val="Calibri"/>
-        <color rgb="FF70AD47"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> y el tiempo atmosférico.</t>
     </r>
@@ -380,25 +393,28 @@
   <si>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD46"/>
         <rFont val="Calibri"/>
-        <color rgb="FF70AD46"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">La luz es la principal señal que sincroniza el reloj interno del cuerpo con el ciclo diurno-nocturno </t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF741B47"/>
         <rFont val="Calibri"/>
-        <color rgb="FF741B47"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t>(día-noche)</t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD46"/>
         <rFont val="Calibri"/>
-        <color rgb="FF70AD46"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> del sol.</t>
     </r>
@@ -499,25 +515,28 @@
   <si>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF00FF"/>
         <rFont val="Calibri"/>
-        <color rgb="FFFF00FF"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">La exposición a la luz </t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF1C4587"/>
         <rFont val="Calibri"/>
-        <color rgb="FF1C4587"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">en horario nocturno </t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF00FF"/>
         <rFont val="Calibri"/>
-        <color rgb="FFFF00FF"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t>le indica al cuerpo que aún es de día. Esto aumenta el estado de alerta y retrasa el reloj interno.</t>
     </r>
@@ -540,17 +559,19 @@
   <si>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD46"/>
         <rFont val="Calibri"/>
-        <color rgb="FF70AD46"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Exponerse a la luz natural (el sol) o a luz eléctrica de alta intensidad, puede reducir el estrés y mejorar el equilibrio emocional, </t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF1C4587"/>
         <rFont val="Calibri"/>
-        <color rgb="FF1C4587"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t>siempre que se evite el deslumbramiento.</t>
     </r>
@@ -633,41 +654,46 @@
   <si>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF00FF"/>
         <rFont val="Calibri"/>
-        <color rgb="FFFF00FF"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Con la edad, </t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD46"/>
         <rFont val="Calibri"/>
-        <color rgb="FF70AD46"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t>el cristalino</t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF00FF"/>
         <rFont val="Calibri"/>
-        <color rgb="FFFF00FF"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> de los ojos se vuelve menos transparentes, lo que puede reducir la respuesta </t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD46"/>
         <rFont val="Calibri"/>
-        <color rgb="FF70AD46"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">del </t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF00FF"/>
         <rFont val="Calibri"/>
-        <color rgb="FFFF00FF"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t>cuerpo a la exposición a la luz.</t>
     </r>
@@ -714,25 +740,28 @@
   <si>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD46"/>
         <rFont val="Calibri"/>
-        <color rgb="FF70AD46"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t>Se necesitan estudios que investiguen la exposici</t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF741B47"/>
         <rFont val="Calibri"/>
-        <color rgb="FF741B47"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t>ón</t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD46"/>
         <rFont val="Calibri"/>
-        <color rgb="FF70AD46"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> a la luz en el mundo real.</t>
     </r>
@@ -782,25 +811,28 @@
   <si>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD47"/>
         <rFont val="Arial"/>
-        <color rgb="FF70AD47"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">La luz es una señal potente para el organismo, ya que afecta a nuestros ritmos circadianos, a la calidad del sueño, al estado de ánimo y al rendimiento </t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF1C4587"/>
         <rFont val="Arial"/>
-        <color rgb="FF1C4587"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t>intelectual</t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD47"/>
         <rFont val="Arial"/>
-        <color rgb="FF70AD47"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -817,25 +849,28 @@
   <si>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD47"/>
         <rFont val="Arial"/>
-        <color rgb="FF70AD47"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">La luz natural durante la mañana y el día favorece aspectos relacionados con la salud, mientras que </t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF134F5C"/>
         <rFont val="Arial"/>
-        <color rgb="FF134F5C"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t>la exposición a la luz artificial en horario nocturno</t>
     </r>
     <r>
       <rPr>
+        <sz val="12"/>
+        <color rgb="FF70AD47"/>
         <rFont val="Arial"/>
-        <color rgb="FF70AD47"/>
-        <sz val="12.0"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> puede resultar disruptora.</t>
     </r>
@@ -851,129 +886,234 @@
   </si>
   <si>
     <t>La gestión de la exposición a la luz forma parte de un estilo de vida saludable, al igual que la dieta, el ejercicio y la higiene del sueño.</t>
+  </si>
+  <si>
+    <t>References</t>
+  </si>
+  <si>
+    <t>Consensus statements</t>
+  </si>
+  <si>
+    <t>Consensus statements (Spanish)</t>
+  </si>
+  <si>
+    <t>Key messages</t>
+  </si>
+  <si>
+    <t>Mensajes clave</t>
+  </si>
+  <si>
+    <t>Referencias</t>
+  </si>
+  <si>
+    <t>Capítulo</t>
+  </si>
+  <si>
+    <t>Declaración</t>
+  </si>
+  <si>
+    <t>Declaración simplificada</t>
+  </si>
+  <si>
+    <t>Información contextual</t>
+  </si>
+  <si>
+    <t>Número</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="30">
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF70AD46"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF70AD46"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF70AD47"/>
       <name val="Noto Sans"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FFFF00FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FFFF00FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF741B47"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF741B47"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF242424"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF741B47"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF242424"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF70AD46"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF70AD47"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FFFF00FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="15.0"/>
+      <sz val="15"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF70AD47"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="9"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FF70AD46"/>
+      <name val="Calibri, sans-serif"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF741B47"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1C4587"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1C4587"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF134F5C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -981,7 +1121,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -990,8 +1130,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
-    <border/>
+  <borders count="11">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -1003,6 +1149,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -1017,6 +1164,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1031,20 +1179,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1059,8 +1194,10 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1070,6 +1207,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1084,6 +1222,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -1098,6 +1237,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -1112,6 +1252,7 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1126,6 +1267,7 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1140,184 +1282,129 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="41">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="2" fontId="15" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="2" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard 2" xfId="1" xr:uid="{0395EDA2-F53C-834E-B9AB-5D83225690F4}"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1507,25 +1594,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.89"/>
-    <col customWidth="1" min="2" max="3" width="16.67"/>
-    <col customWidth="1" min="4" max="4" width="21.44"/>
-    <col customWidth="1" min="5" max="5" width="33.22"/>
-    <col customWidth="1" min="6" max="6" width="31.22"/>
-    <col customWidth="1" min="7" max="26" width="8.33"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="21.5" customWidth="1"/>
+    <col min="5" max="5" width="33.1640625" customWidth="1"/>
+    <col min="6" max="6" width="31.1640625" customWidth="1"/>
+    <col min="7" max="26" width="8.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1565,7 +1652,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -1605,7 +1692,7 @@
       <c r="Y2" s="6"/>
       <c r="Z2" s="6"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1">
       <c r="A3" s="7" t="s">
         <v>12</v>
       </c>
@@ -1645,21 +1732,21 @@
       <c r="Y3" s="6"/>
       <c r="Z3" s="6"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G4" s="6"/>
@@ -1683,23 +1770,23 @@
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="9" t="s">
         <v>27</v>
       </c>
       <c r="G5" s="6"/>
@@ -1723,7 +1810,7 @@
       <c r="Y5" s="6"/>
       <c r="Z5" s="6"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:26" ht="15.75" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1751,7 +1838,7 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:26" ht="15.75" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1779,7 +1866,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:26" ht="15.75" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1807,7 +1894,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:26" ht="15.75" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -1835,7 +1922,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:26" ht="15.75" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -1863,7 +1950,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:26" ht="15.75" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1891,7 +1978,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:26" ht="15.75" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1919,7 +2006,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:26" ht="15.75" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1947,7 +2034,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" spans="1:26" ht="15.75" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1975,7 +2062,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" spans="1:26" ht="15.75" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2003,7 +2090,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2031,7 +2118,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:26" ht="15.75" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2059,7 +2146,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="1:26" ht="15.75" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2087,7 +2174,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" spans="1:26" ht="15.75" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2115,7 +2202,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="1:26" ht="15.75" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2143,7 +2230,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:26" ht="15.75" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2171,7 +2258,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:26" ht="15.75" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2199,7 +2286,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:26" ht="15.75" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2227,7 +2314,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:26" ht="15.75" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2255,7 +2342,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:26" ht="15.75" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2283,7 +2370,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:26" ht="15.75" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2311,7 +2398,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:26" ht="15.75" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2339,7 +2426,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:26" ht="15.75" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -2367,7 +2454,7 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:26" ht="15.75" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -2395,7 +2482,7 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:26" ht="15.75" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -2423,7 +2510,7 @@
       <c r="Y30" s="2"/>
       <c r="Z30" s="2"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:26" ht="15.75" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -2451,7 +2538,7 @@
       <c r="Y31" s="2"/>
       <c r="Z31" s="2"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:26" ht="15.75" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -2479,7 +2566,7 @@
       <c r="Y32" s="2"/>
       <c r="Z32" s="2"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:26" ht="15.75" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -2507,7 +2594,7 @@
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:26" ht="15.75" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -2535,7 +2622,7 @@
       <c r="Y34" s="2"/>
       <c r="Z34" s="2"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:26" ht="15.75" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -2563,7 +2650,7 @@
       <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:26" ht="15.75" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -2591,7 +2678,7 @@
       <c r="Y36" s="2"/>
       <c r="Z36" s="2"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:26" ht="15.75" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -2619,7 +2706,7 @@
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:26" ht="15.75" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -2647,7 +2734,7 @@
       <c r="Y38" s="2"/>
       <c r="Z38" s="2"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:26" ht="15.75" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -2675,7 +2762,7 @@
       <c r="Y39" s="2"/>
       <c r="Z39" s="2"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:26" ht="15.75" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2703,7 +2790,7 @@
       <c r="Y40" s="2"/>
       <c r="Z40" s="2"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:26" ht="15.75" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -2731,7 +2818,7 @@
       <c r="Y41" s="2"/>
       <c r="Z41" s="2"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:26" ht="15.75" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2759,7 +2846,7 @@
       <c r="Y42" s="2"/>
       <c r="Z42" s="2"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:26" ht="15.75" customHeight="1">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -2787,7 +2874,7 @@
       <c r="Y43" s="2"/>
       <c r="Z43" s="2"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:26" ht="15.75" customHeight="1">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -2815,7 +2902,7 @@
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:26" ht="15.75" customHeight="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -2843,7 +2930,7 @@
       <c r="Y45" s="2"/>
       <c r="Z45" s="2"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:26" ht="15.75" customHeight="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -2871,7 +2958,7 @@
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:26" ht="15.75" customHeight="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -2899,7 +2986,7 @@
       <c r="Y47" s="2"/>
       <c r="Z47" s="2"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:26" ht="15.75" customHeight="1">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -2927,7 +3014,7 @@
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:26" ht="15.75" customHeight="1">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -2955,7 +3042,7 @@
       <c r="Y49" s="2"/>
       <c r="Z49" s="2"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:26" ht="15.75" customHeight="1">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2983,7 +3070,7 @@
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:26" ht="15.75" customHeight="1">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -3011,7 +3098,7 @@
       <c r="Y51" s="2"/>
       <c r="Z51" s="2"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:26" ht="15.75" customHeight="1">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -3039,7 +3126,7 @@
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:26" ht="15.75" customHeight="1">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -3067,7 +3154,7 @@
       <c r="Y53" s="2"/>
       <c r="Z53" s="2"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:26" ht="15.75" customHeight="1">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -3095,7 +3182,7 @@
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:26" ht="15.75" customHeight="1">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -3123,7 +3210,7 @@
       <c r="Y55" s="2"/>
       <c r="Z55" s="2"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:26" ht="15.75" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -3151,7 +3238,7 @@
       <c r="Y56" s="2"/>
       <c r="Z56" s="2"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:26" ht="15.75" customHeight="1">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -3179,7 +3266,7 @@
       <c r="Y57" s="2"/>
       <c r="Z57" s="2"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:26" ht="15.75" customHeight="1">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -3207,7 +3294,7 @@
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:26" ht="15.75" customHeight="1">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -3235,7 +3322,7 @@
       <c r="Y59" s="2"/>
       <c r="Z59" s="2"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:26" ht="15.75" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -3263,7 +3350,7 @@
       <c r="Y60" s="2"/>
       <c r="Z60" s="2"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:26" ht="15.75" customHeight="1">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -3291,7 +3378,7 @@
       <c r="Y61" s="2"/>
       <c r="Z61" s="2"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:26" ht="15.75" customHeight="1">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -3319,7 +3406,7 @@
       <c r="Y62" s="2"/>
       <c r="Z62" s="2"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:26" ht="15.75" customHeight="1">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3347,7 +3434,7 @@
       <c r="Y63" s="2"/>
       <c r="Z63" s="2"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:26" ht="15.75" customHeight="1">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -3375,7 +3462,7 @@
       <c r="Y64" s="2"/>
       <c r="Z64" s="2"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:26" ht="15.75" customHeight="1">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -3403,7 +3490,7 @@
       <c r="Y65" s="2"/>
       <c r="Z65" s="2"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:26" ht="15.75" customHeight="1">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -3431,7 +3518,7 @@
       <c r="Y66" s="2"/>
       <c r="Z66" s="2"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:26" ht="15.75" customHeight="1">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -3459,7 +3546,7 @@
       <c r="Y67" s="2"/>
       <c r="Z67" s="2"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:26" ht="15.75" customHeight="1">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -3487,7 +3574,7 @@
       <c r="Y68" s="2"/>
       <c r="Z68" s="2"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:26" ht="15.75" customHeight="1">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -3515,7 +3602,7 @@
       <c r="Y69" s="2"/>
       <c r="Z69" s="2"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:26" ht="15.75" customHeight="1">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -3543,7 +3630,7 @@
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:26" ht="15.75" customHeight="1">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -3571,7 +3658,7 @@
       <c r="Y71" s="2"/>
       <c r="Z71" s="2"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:26" ht="15.75" customHeight="1">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -3599,7 +3686,7 @@
       <c r="Y72" s="2"/>
       <c r="Z72" s="2"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:26" ht="15.75" customHeight="1">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -3627,7 +3714,7 @@
       <c r="Y73" s="2"/>
       <c r="Z73" s="2"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:26" ht="15.75" customHeight="1">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -3655,7 +3742,7 @@
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:26" ht="15.75" customHeight="1">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -3683,7 +3770,7 @@
       <c r="Y75" s="2"/>
       <c r="Z75" s="2"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:26" ht="15.75" customHeight="1">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -3711,7 +3798,7 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:26" ht="15.75" customHeight="1">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -3739,7 +3826,7 @@
       <c r="Y77" s="2"/>
       <c r="Z77" s="2"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:26" ht="15.75" customHeight="1">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -3767,7 +3854,7 @@
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:26" ht="15.75" customHeight="1">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -3795,7 +3882,7 @@
       <c r="Y79" s="2"/>
       <c r="Z79" s="2"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:26" ht="15.75" customHeight="1">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -3823,7 +3910,7 @@
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:26" ht="15.75" customHeight="1">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -3851,7 +3938,7 @@
       <c r="Y81" s="2"/>
       <c r="Z81" s="2"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:26" ht="15.75" customHeight="1">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -3879,7 +3966,7 @@
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:26" ht="15.75" customHeight="1">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -3907,7 +3994,7 @@
       <c r="Y83" s="2"/>
       <c r="Z83" s="2"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:26" ht="15.75" customHeight="1">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -3935,7 +4022,7 @@
       <c r="Y84" s="2"/>
       <c r="Z84" s="2"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:26" ht="15.75" customHeight="1">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -3963,7 +4050,7 @@
       <c r="Y85" s="2"/>
       <c r="Z85" s="2"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:26" ht="15.75" customHeight="1">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -3991,7 +4078,7 @@
       <c r="Y86" s="2"/>
       <c r="Z86" s="2"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:26" ht="15.75" customHeight="1">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -4019,7 +4106,7 @@
       <c r="Y87" s="2"/>
       <c r="Z87" s="2"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:26" ht="15.75" customHeight="1">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -4047,7 +4134,7 @@
       <c r="Y88" s="2"/>
       <c r="Z88" s="2"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:26" ht="15.75" customHeight="1">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -4075,7 +4162,7 @@
       <c r="Y89" s="2"/>
       <c r="Z89" s="2"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:26" ht="15.75" customHeight="1">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -4103,7 +4190,7 @@
       <c r="Y90" s="2"/>
       <c r="Z90" s="2"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:26" ht="15.75" customHeight="1">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -4131,7 +4218,7 @@
       <c r="Y91" s="2"/>
       <c r="Z91" s="2"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:26" ht="15.75" customHeight="1">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -4159,7 +4246,7 @@
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:26" ht="15.75" customHeight="1">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -4187,7 +4274,7 @@
       <c r="Y93" s="2"/>
       <c r="Z93" s="2"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:26" ht="15.75" customHeight="1">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -4215,7 +4302,7 @@
       <c r="Y94" s="2"/>
       <c r="Z94" s="2"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:26" ht="15.75" customHeight="1">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -4243,7 +4330,7 @@
       <c r="Y95" s="2"/>
       <c r="Z95" s="2"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:26" ht="15.75" customHeight="1">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -4271,7 +4358,7 @@
       <c r="Y96" s="2"/>
       <c r="Z96" s="2"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:26" ht="15.75" customHeight="1">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -4299,7 +4386,7 @@
       <c r="Y97" s="2"/>
       <c r="Z97" s="2"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="1:26" ht="15.75" customHeight="1">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -4327,7 +4414,7 @@
       <c r="Y98" s="2"/>
       <c r="Z98" s="2"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="1:26" ht="15.75" customHeight="1">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -4355,7 +4442,7 @@
       <c r="Y99" s="2"/>
       <c r="Z99" s="2"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="1:26" ht="15.75" customHeight="1">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -4383,7 +4470,7 @@
       <c r="Y100" s="2"/>
       <c r="Z100" s="2"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="1:26" ht="15.75" customHeight="1">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -4411,7 +4498,7 @@
       <c r="Y101" s="2"/>
       <c r="Z101" s="2"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="1:26" ht="15.75" customHeight="1">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -4439,7 +4526,7 @@
       <c r="Y102" s="2"/>
       <c r="Z102" s="2"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="1:26" ht="15.75" customHeight="1">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -4467,7 +4554,7 @@
       <c r="Y103" s="2"/>
       <c r="Z103" s="2"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="1:26" ht="15.75" customHeight="1">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -4495,7 +4582,7 @@
       <c r="Y104" s="2"/>
       <c r="Z104" s="2"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="1:26" ht="15.75" customHeight="1">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -4523,7 +4610,7 @@
       <c r="Y105" s="2"/>
       <c r="Z105" s="2"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="1:26" ht="15.75" customHeight="1">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -4551,7 +4638,7 @@
       <c r="Y106" s="2"/>
       <c r="Z106" s="2"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="1:26" ht="15.75" customHeight="1">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -4579,7 +4666,7 @@
       <c r="Y107" s="2"/>
       <c r="Z107" s="2"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="1:26" ht="15.75" customHeight="1">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -4607,7 +4694,7 @@
       <c r="Y108" s="2"/>
       <c r="Z108" s="2"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="1:26" ht="15.75" customHeight="1">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -4635,7 +4722,7 @@
       <c r="Y109" s="2"/>
       <c r="Z109" s="2"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="1:26" ht="15.75" customHeight="1">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -4663,7 +4750,7 @@
       <c r="Y110" s="2"/>
       <c r="Z110" s="2"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="1:26" ht="15.75" customHeight="1">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -4691,7 +4778,7 @@
       <c r="Y111" s="2"/>
       <c r="Z111" s="2"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="1:26" ht="15.75" customHeight="1">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -4719,7 +4806,7 @@
       <c r="Y112" s="2"/>
       <c r="Z112" s="2"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="1:26" ht="15.75" customHeight="1">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -4747,7 +4834,7 @@
       <c r="Y113" s="2"/>
       <c r="Z113" s="2"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:26" ht="15.75" customHeight="1">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -4775,7 +4862,7 @@
       <c r="Y114" s="2"/>
       <c r="Z114" s="2"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="1:26" ht="15.75" customHeight="1">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -4803,7 +4890,7 @@
       <c r="Y115" s="2"/>
       <c r="Z115" s="2"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="1:26" ht="15.75" customHeight="1">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -4831,7 +4918,7 @@
       <c r="Y116" s="2"/>
       <c r="Z116" s="2"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="1:26" ht="15.75" customHeight="1">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -4859,7 +4946,7 @@
       <c r="Y117" s="2"/>
       <c r="Z117" s="2"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="1:26" ht="15.75" customHeight="1">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -4887,7 +4974,7 @@
       <c r="Y118" s="2"/>
       <c r="Z118" s="2"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="1:26" ht="15.75" customHeight="1">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -4915,7 +5002,7 @@
       <c r="Y119" s="2"/>
       <c r="Z119" s="2"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="1:26" ht="15.75" customHeight="1">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -4943,7 +5030,7 @@
       <c r="Y120" s="2"/>
       <c r="Z120" s="2"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="1:26" ht="15.75" customHeight="1">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -4971,7 +5058,7 @@
       <c r="Y121" s="2"/>
       <c r="Z121" s="2"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="1:26" ht="15.75" customHeight="1">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -4999,7 +5086,7 @@
       <c r="Y122" s="2"/>
       <c r="Z122" s="2"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="1:26" ht="15.75" customHeight="1">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -5027,7 +5114,7 @@
       <c r="Y123" s="2"/>
       <c r="Z123" s="2"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="1:26" ht="15.75" customHeight="1">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -5055,7 +5142,7 @@
       <c r="Y124" s="2"/>
       <c r="Z124" s="2"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="1:26" ht="15.75" customHeight="1">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -5083,7 +5170,7 @@
       <c r="Y125" s="2"/>
       <c r="Z125" s="2"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="1:26" ht="15.75" customHeight="1">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -5111,7 +5198,7 @@
       <c r="Y126" s="2"/>
       <c r="Z126" s="2"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="1:26" ht="15.75" customHeight="1">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -5139,7 +5226,7 @@
       <c r="Y127" s="2"/>
       <c r="Z127" s="2"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="1:26" ht="15.75" customHeight="1">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -5167,7 +5254,7 @@
       <c r="Y128" s="2"/>
       <c r="Z128" s="2"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" spans="1:26" ht="15.75" customHeight="1">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -5195,7 +5282,7 @@
       <c r="Y129" s="2"/>
       <c r="Z129" s="2"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" spans="1:26" ht="15.75" customHeight="1">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -5223,7 +5310,7 @@
       <c r="Y130" s="2"/>
       <c r="Z130" s="2"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" spans="1:26" ht="15.75" customHeight="1">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -5251,7 +5338,7 @@
       <c r="Y131" s="2"/>
       <c r="Z131" s="2"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" spans="1:26" ht="15.75" customHeight="1">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -5279,7 +5366,7 @@
       <c r="Y132" s="2"/>
       <c r="Z132" s="2"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" spans="1:26" ht="15.75" customHeight="1">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -5307,7 +5394,7 @@
       <c r="Y133" s="2"/>
       <c r="Z133" s="2"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" spans="1:26" ht="15.75" customHeight="1">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -5335,7 +5422,7 @@
       <c r="Y134" s="2"/>
       <c r="Z134" s="2"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" spans="1:26" ht="15.75" customHeight="1">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -5363,7 +5450,7 @@
       <c r="Y135" s="2"/>
       <c r="Z135" s="2"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" spans="1:26" ht="15.75" customHeight="1">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -5391,7 +5478,7 @@
       <c r="Y136" s="2"/>
       <c r="Z136" s="2"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" spans="1:26" ht="15.75" customHeight="1">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -5419,7 +5506,7 @@
       <c r="Y137" s="2"/>
       <c r="Z137" s="2"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" spans="1:26" ht="15.75" customHeight="1">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -5447,7 +5534,7 @@
       <c r="Y138" s="2"/>
       <c r="Z138" s="2"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" spans="1:26" ht="15.75" customHeight="1">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -5475,7 +5562,7 @@
       <c r="Y139" s="2"/>
       <c r="Z139" s="2"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="1:26" ht="15.75" customHeight="1">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -5503,7 +5590,7 @@
       <c r="Y140" s="2"/>
       <c r="Z140" s="2"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" spans="1:26" ht="15.75" customHeight="1">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -5531,7 +5618,7 @@
       <c r="Y141" s="2"/>
       <c r="Z141" s="2"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" spans="1:26" ht="15.75" customHeight="1">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -5559,7 +5646,7 @@
       <c r="Y142" s="2"/>
       <c r="Z142" s="2"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" spans="1:26" ht="15.75" customHeight="1">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -5587,7 +5674,7 @@
       <c r="Y143" s="2"/>
       <c r="Z143" s="2"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" spans="1:26" ht="15.75" customHeight="1">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -5615,7 +5702,7 @@
       <c r="Y144" s="2"/>
       <c r="Z144" s="2"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" spans="1:26" ht="15.75" customHeight="1">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -5643,7 +5730,7 @@
       <c r="Y145" s="2"/>
       <c r="Z145" s="2"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" spans="1:26" ht="15.75" customHeight="1">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -5671,7 +5758,7 @@
       <c r="Y146" s="2"/>
       <c r="Z146" s="2"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" spans="1:26" ht="15.75" customHeight="1">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -5699,7 +5786,7 @@
       <c r="Y147" s="2"/>
       <c r="Z147" s="2"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="1:26" ht="15.75" customHeight="1">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -5727,7 +5814,7 @@
       <c r="Y148" s="2"/>
       <c r="Z148" s="2"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" spans="1:26" ht="15.75" customHeight="1">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -5755,7 +5842,7 @@
       <c r="Y149" s="2"/>
       <c r="Z149" s="2"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" spans="1:26" ht="15.75" customHeight="1">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -5783,7 +5870,7 @@
       <c r="Y150" s="2"/>
       <c r="Z150" s="2"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" spans="1:26" ht="15.75" customHeight="1">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -5811,7 +5898,7 @@
       <c r="Y151" s="2"/>
       <c r="Z151" s="2"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" spans="1:26" ht="15.75" customHeight="1">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -5839,7 +5926,7 @@
       <c r="Y152" s="2"/>
       <c r="Z152" s="2"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" spans="1:26" ht="15.75" customHeight="1">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -5867,7 +5954,7 @@
       <c r="Y153" s="2"/>
       <c r="Z153" s="2"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" spans="1:26" ht="15.75" customHeight="1">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -5895,7 +5982,7 @@
       <c r="Y154" s="2"/>
       <c r="Z154" s="2"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" spans="1:26" ht="15.75" customHeight="1">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -5923,7 +6010,7 @@
       <c r="Y155" s="2"/>
       <c r="Z155" s="2"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" spans="1:26" ht="15.75" customHeight="1">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -5951,7 +6038,7 @@
       <c r="Y156" s="2"/>
       <c r="Z156" s="2"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" spans="1:26" ht="15.75" customHeight="1">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -5979,7 +6066,7 @@
       <c r="Y157" s="2"/>
       <c r="Z157" s="2"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" spans="1:26" ht="15.75" customHeight="1">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -6007,7 +6094,7 @@
       <c r="Y158" s="2"/>
       <c r="Z158" s="2"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" spans="1:26" ht="15.75" customHeight="1">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -6035,7 +6122,7 @@
       <c r="Y159" s="2"/>
       <c r="Z159" s="2"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" spans="1:26" ht="15.75" customHeight="1">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -6063,7 +6150,7 @@
       <c r="Y160" s="2"/>
       <c r="Z160" s="2"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" spans="1:26" ht="15.75" customHeight="1">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -6091,7 +6178,7 @@
       <c r="Y161" s="2"/>
       <c r="Z161" s="2"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" spans="1:26" ht="15.75" customHeight="1">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -6119,7 +6206,7 @@
       <c r="Y162" s="2"/>
       <c r="Z162" s="2"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" spans="1:26" ht="15.75" customHeight="1">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -6147,7 +6234,7 @@
       <c r="Y163" s="2"/>
       <c r="Z163" s="2"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" spans="1:26" ht="15.75" customHeight="1">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -6175,7 +6262,7 @@
       <c r="Y164" s="2"/>
       <c r="Z164" s="2"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" spans="1:26" ht="15.75" customHeight="1">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -6203,7 +6290,7 @@
       <c r="Y165" s="2"/>
       <c r="Z165" s="2"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" spans="1:26" ht="15.75" customHeight="1">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -6231,7 +6318,7 @@
       <c r="Y166" s="2"/>
       <c r="Z166" s="2"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" spans="1:26" ht="15.75" customHeight="1">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -6259,7 +6346,7 @@
       <c r="Y167" s="2"/>
       <c r="Z167" s="2"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" spans="1:26" ht="15.75" customHeight="1">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -6287,7 +6374,7 @@
       <c r="Y168" s="2"/>
       <c r="Z168" s="2"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" spans="1:26" ht="15.75" customHeight="1">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -6315,7 +6402,7 @@
       <c r="Y169" s="2"/>
       <c r="Z169" s="2"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" spans="1:26" ht="15.75" customHeight="1">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -6343,7 +6430,7 @@
       <c r="Y170" s="2"/>
       <c r="Z170" s="2"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" spans="1:26" ht="15.75" customHeight="1">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -6371,7 +6458,7 @@
       <c r="Y171" s="2"/>
       <c r="Z171" s="2"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" spans="1:26" ht="15.75" customHeight="1">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -6399,7 +6486,7 @@
       <c r="Y172" s="2"/>
       <c r="Z172" s="2"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" spans="1:26" ht="15.75" customHeight="1">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -6427,7 +6514,7 @@
       <c r="Y173" s="2"/>
       <c r="Z173" s="2"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" spans="1:26" ht="15.75" customHeight="1">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -6455,7 +6542,7 @@
       <c r="Y174" s="2"/>
       <c r="Z174" s="2"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" spans="1:26" ht="15.75" customHeight="1">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -6483,7 +6570,7 @@
       <c r="Y175" s="2"/>
       <c r="Z175" s="2"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" spans="1:26" ht="15.75" customHeight="1">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -6511,7 +6598,7 @@
       <c r="Y176" s="2"/>
       <c r="Z176" s="2"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" spans="1:26" ht="15.75" customHeight="1">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -6539,7 +6626,7 @@
       <c r="Y177" s="2"/>
       <c r="Z177" s="2"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" spans="1:26" ht="15.75" customHeight="1">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -6567,7 +6654,7 @@
       <c r="Y178" s="2"/>
       <c r="Z178" s="2"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" spans="1:26" ht="15.75" customHeight="1">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -6595,7 +6682,7 @@
       <c r="Y179" s="2"/>
       <c r="Z179" s="2"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" spans="1:26" ht="15.75" customHeight="1">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -6623,7 +6710,7 @@
       <c r="Y180" s="2"/>
       <c r="Z180" s="2"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" spans="1:26" ht="15.75" customHeight="1">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -6651,7 +6738,7 @@
       <c r="Y181" s="2"/>
       <c r="Z181" s="2"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" spans="1:26" ht="15.75" customHeight="1">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -6679,7 +6766,7 @@
       <c r="Y182" s="2"/>
       <c r="Z182" s="2"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" spans="1:26" ht="15.75" customHeight="1">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -6707,7 +6794,7 @@
       <c r="Y183" s="2"/>
       <c r="Z183" s="2"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" spans="1:26" ht="15.75" customHeight="1">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -6735,7 +6822,7 @@
       <c r="Y184" s="2"/>
       <c r="Z184" s="2"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" spans="1:26" ht="15.75" customHeight="1">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -6763,7 +6850,7 @@
       <c r="Y185" s="2"/>
       <c r="Z185" s="2"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" spans="1:26" ht="15.75" customHeight="1">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -6791,7 +6878,7 @@
       <c r="Y186" s="2"/>
       <c r="Z186" s="2"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" spans="1:26" ht="15.75" customHeight="1">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -6819,7 +6906,7 @@
       <c r="Y187" s="2"/>
       <c r="Z187" s="2"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" spans="1:26" ht="15.75" customHeight="1">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -6847,7 +6934,7 @@
       <c r="Y188" s="2"/>
       <c r="Z188" s="2"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" spans="1:26" ht="15.75" customHeight="1">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -6875,7 +6962,7 @@
       <c r="Y189" s="2"/>
       <c r="Z189" s="2"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" spans="1:26" ht="15.75" customHeight="1">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -6903,7 +6990,7 @@
       <c r="Y190" s="2"/>
       <c r="Z190" s="2"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" spans="1:26" ht="15.75" customHeight="1">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -6931,7 +7018,7 @@
       <c r="Y191" s="2"/>
       <c r="Z191" s="2"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" spans="1:26" ht="15.75" customHeight="1">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -6959,7 +7046,7 @@
       <c r="Y192" s="2"/>
       <c r="Z192" s="2"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" spans="1:26" ht="15.75" customHeight="1">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -6987,7 +7074,7 @@
       <c r="Y193" s="2"/>
       <c r="Z193" s="2"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" spans="1:26" ht="15.75" customHeight="1">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -7015,7 +7102,7 @@
       <c r="Y194" s="2"/>
       <c r="Z194" s="2"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" spans="1:26" ht="15.75" customHeight="1">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -7043,7 +7130,7 @@
       <c r="Y195" s="2"/>
       <c r="Z195" s="2"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" spans="1:26" ht="15.75" customHeight="1">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -7071,7 +7158,7 @@
       <c r="Y196" s="2"/>
       <c r="Z196" s="2"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" spans="1:26" ht="15.75" customHeight="1">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -7099,7 +7186,7 @@
       <c r="Y197" s="2"/>
       <c r="Z197" s="2"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" spans="1:26" ht="15.75" customHeight="1">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -7127,7 +7214,7 @@
       <c r="Y198" s="2"/>
       <c r="Z198" s="2"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" spans="1:26" ht="15.75" customHeight="1">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -7155,7 +7242,7 @@
       <c r="Y199" s="2"/>
       <c r="Z199" s="2"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" spans="1:26" ht="15.75" customHeight="1">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -7183,7 +7270,7 @@
       <c r="Y200" s="2"/>
       <c r="Z200" s="2"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" spans="1:26" ht="15.75" customHeight="1">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -7211,7 +7298,7 @@
       <c r="Y201" s="2"/>
       <c r="Z201" s="2"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" spans="1:26" ht="15.75" customHeight="1">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -7239,7 +7326,7 @@
       <c r="Y202" s="2"/>
       <c r="Z202" s="2"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" spans="1:26" ht="15.75" customHeight="1">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -7267,7 +7354,7 @@
       <c r="Y203" s="2"/>
       <c r="Z203" s="2"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" spans="1:26" ht="15.75" customHeight="1">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -7295,7 +7382,7 @@
       <c r="Y204" s="2"/>
       <c r="Z204" s="2"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" spans="1:26" ht="15.75" customHeight="1">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -7323,7 +7410,7 @@
       <c r="Y205" s="2"/>
       <c r="Z205" s="2"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" spans="1:26" ht="15.75" customHeight="1">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -7351,7 +7438,7 @@
       <c r="Y206" s="2"/>
       <c r="Z206" s="2"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" spans="1:26" ht="15.75" customHeight="1">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -7379,7 +7466,7 @@
       <c r="Y207" s="2"/>
       <c r="Z207" s="2"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" spans="1:26" ht="15.75" customHeight="1">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -7407,7 +7494,7 @@
       <c r="Y208" s="2"/>
       <c r="Z208" s="2"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" spans="1:26" ht="15.75" customHeight="1">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -7435,7 +7522,7 @@
       <c r="Y209" s="2"/>
       <c r="Z209" s="2"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" spans="1:26" ht="15.75" customHeight="1">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -7463,7 +7550,7 @@
       <c r="Y210" s="2"/>
       <c r="Z210" s="2"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" spans="1:26" ht="15.75" customHeight="1">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -7491,7 +7578,7 @@
       <c r="Y211" s="2"/>
       <c r="Z211" s="2"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" spans="1:26" ht="15.75" customHeight="1">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -7519,7 +7606,7 @@
       <c r="Y212" s="2"/>
       <c r="Z212" s="2"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" spans="1:26" ht="15.75" customHeight="1">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -7547,7 +7634,7 @@
       <c r="Y213" s="2"/>
       <c r="Z213" s="2"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" spans="1:26" ht="15.75" customHeight="1">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -7575,7 +7662,7 @@
       <c r="Y214" s="2"/>
       <c r="Z214" s="2"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" spans="1:26" ht="15.75" customHeight="1">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -7603,7 +7690,7 @@
       <c r="Y215" s="2"/>
       <c r="Z215" s="2"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" spans="1:26" ht="15.75" customHeight="1">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -7631,7 +7718,7 @@
       <c r="Y216" s="2"/>
       <c r="Z216" s="2"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" spans="1:26" ht="15.75" customHeight="1">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -7659,7 +7746,7 @@
       <c r="Y217" s="2"/>
       <c r="Z217" s="2"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" spans="1:26" ht="15.75" customHeight="1">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -7687,7 +7774,7 @@
       <c r="Y218" s="2"/>
       <c r="Z218" s="2"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" spans="1:26" ht="15.75" customHeight="1">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -7715,7 +7802,7 @@
       <c r="Y219" s="2"/>
       <c r="Z219" s="2"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" spans="1:26" ht="15.75" customHeight="1">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -7743,10 +7830,10 @@
       <c r="Y220" s="2"/>
       <c r="Z220" s="2"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="221" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="222" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="223" spans="1:26" ht="15.75" customHeight="1"/>
+    <row r="224" spans="1:26" ht="15.75" customHeight="1"/>
     <row r="225" ht="15.75" customHeight="1"/>
     <row r="226" ht="15.75" customHeight="1"/>
     <row r="227" ht="15.75" customHeight="1"/>
@@ -8525,1442 +8612,1519 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="D2"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:AA1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="38.67"/>
-    <col customWidth="1" min="2" max="2" width="19.56"/>
-    <col customWidth="1" min="3" max="3" width="7.78"/>
-    <col customWidth="1" min="4" max="9" width="32.89"/>
-    <col customWidth="1" min="10" max="26" width="8.89"/>
+    <col min="1" max="1" width="38.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19.5" customWidth="1"/>
+    <col min="3" max="4" width="7.83203125" customWidth="1"/>
+    <col min="5" max="10" width="32.83203125" customWidth="1"/>
+    <col min="11" max="27" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:27" ht="15.75" customHeight="1">
+      <c r="A1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="15" t="s">
+      <c r="B1" s="39" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="39" t="s">
+        <v>221</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="39" t="s">
+        <v>219</v>
+      </c>
+      <c r="I1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" ht="283.5" customHeight="1">
-      <c r="A2" s="13" t="s">
+      <c r="J1" s="39" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="283.5" customHeight="1">
+      <c r="A2" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="20">
-        <v>1.0</v>
-      </c>
-      <c r="D2" s="21" t="s">
+      <c r="C2" s="16">
+        <v>1</v>
+      </c>
+      <c r="D2" s="16">
+        <v>1</v>
+      </c>
+      <c r="E2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="F2" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="G2" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="H2" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="I2" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="24" t="s">
+      <c r="J2" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="25"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-      <c r="V2" s="25"/>
-      <c r="W2" s="25"/>
-      <c r="X2" s="25"/>
-      <c r="Y2" s="25"/>
-      <c r="Z2" s="25"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="s">
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20"/>
+    </row>
+    <row r="3" spans="1:27" ht="136">
+      <c r="A3" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="20">
-        <v>2.0</v>
-      </c>
-      <c r="D3" s="21" t="s">
+      <c r="C3" s="16">
+        <v>2</v>
+      </c>
+      <c r="D3" s="16">
+        <v>2</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="F3" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="G3" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="H3" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="I3" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="27" t="s">
+      <c r="J3" s="19" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:27" ht="187">
+      <c r="A4" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="20">
-        <v>3.0</v>
-      </c>
-      <c r="D4" s="21" t="s">
+      <c r="C4" s="16">
+        <v>3</v>
+      </c>
+      <c r="D4" s="16">
+        <v>3</v>
+      </c>
+      <c r="E4" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F4" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="G4" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="26" t="s">
+      <c r="H4" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="H4" s="21" t="s">
+      <c r="I4" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="J4" s="21" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:27" ht="136">
+      <c r="A5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="29">
-        <v>4.0</v>
-      </c>
-      <c r="D5" s="21" t="s">
+      <c r="C5" s="22">
+        <v>4</v>
+      </c>
+      <c r="D5" s="22">
+        <v>4</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="F5" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="G5" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="26" t="s">
+      <c r="H5" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="I5" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="J5" s="19" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="s">
+    <row r="6" spans="1:27" ht="170">
+      <c r="A6" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="29">
-        <v>5.0</v>
-      </c>
-      <c r="D6" s="21" t="s">
+      <c r="C6" s="22">
+        <v>5</v>
+      </c>
+      <c r="D6" s="22">
+        <v>5</v>
+      </c>
+      <c r="E6" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="F6" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="G6" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="H6" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="I6" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="I6" s="27" t="s">
+      <c r="J6" s="19" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="13" t="s">
+    <row r="7" spans="1:27" ht="85">
+      <c r="A7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="29">
-        <v>6.0</v>
-      </c>
-      <c r="D7" s="21" t="s">
+      <c r="C7" s="22">
+        <v>6</v>
+      </c>
+      <c r="D7" s="22">
+        <v>6</v>
+      </c>
+      <c r="E7" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="F7" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="G7" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="H7" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="I7" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="32" t="s">
+      <c r="J7" s="25" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="13" t="s">
+    <row r="8" spans="1:27" ht="136">
+      <c r="A8" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="29">
-        <v>7.0</v>
-      </c>
-      <c r="D8" s="21" t="s">
+      <c r="C8" s="22">
+        <v>7</v>
+      </c>
+      <c r="D8" s="22">
+        <v>7</v>
+      </c>
+      <c r="E8" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="F8" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="G8" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="G8" s="33" t="s">
+      <c r="H8" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="23" t="s">
+      <c r="I8" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="J8" s="25" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="s">
+    <row r="9" spans="1:27" ht="102">
+      <c r="A9" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="29">
-        <v>8.0</v>
-      </c>
-      <c r="D9" s="21" t="s">
+      <c r="C9" s="22">
+        <v>8</v>
+      </c>
+      <c r="D9" s="22">
+        <v>8</v>
+      </c>
+      <c r="E9" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="F9" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="G9" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="G9" s="33" t="s">
+      <c r="H9" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="I9" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="I9" s="32" t="s">
+      <c r="J9" s="25" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="s">
+    <row r="10" spans="1:27" ht="51">
+      <c r="A10" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="29">
-        <v>9.0</v>
-      </c>
-      <c r="D10" s="21" t="s">
+      <c r="C10" s="22">
+        <v>9</v>
+      </c>
+      <c r="D10" s="22">
+        <v>9</v>
+      </c>
+      <c r="E10" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="F10" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="G10" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="33" t="s">
+      <c r="H10" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="I10" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="I10" s="35" t="s">
+      <c r="J10" s="26" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:27" ht="85">
+      <c r="A11" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="29">
-        <v>10.0</v>
-      </c>
-      <c r="D11" s="21" t="s">
+      <c r="C11" s="22">
+        <v>10</v>
+      </c>
+      <c r="D11" s="22">
+        <v>10</v>
+      </c>
+      <c r="E11" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="F11" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="G11" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="G11" s="33" t="s">
+      <c r="H11" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="I11" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="I11" s="36" t="s">
+      <c r="J11" s="27" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="13" t="s">
+    <row r="12" spans="1:27" ht="136">
+      <c r="A12" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="29">
-        <v>11.0</v>
-      </c>
-      <c r="D12" s="21" t="s">
+      <c r="C12" s="22">
+        <v>11</v>
+      </c>
+      <c r="D12" s="22">
+        <v>11</v>
+      </c>
+      <c r="E12" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="F12" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="G12" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="G12" s="37" t="s">
+      <c r="H12" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="I12" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="I12" s="38" t="s">
+      <c r="J12" s="27" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="13" t="s">
+    <row r="13" spans="1:27" ht="85">
+      <c r="A13" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="29">
-        <v>12.0</v>
-      </c>
-      <c r="D13" s="21" t="s">
+      <c r="C13" s="22">
+        <v>12</v>
+      </c>
+      <c r="D13" s="22">
+        <v>12</v>
+      </c>
+      <c r="E13" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="F13" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="G13" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="H13" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="I13" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="I13" s="39" t="s">
+      <c r="J13" s="28" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="13" t="s">
+    <row r="14" spans="1:27" ht="68">
+      <c r="A14" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C14" s="29">
-        <v>13.0</v>
-      </c>
-      <c r="D14" s="21" t="s">
+      <c r="C14" s="22">
+        <v>13</v>
+      </c>
+      <c r="D14" s="22">
+        <v>13</v>
+      </c>
+      <c r="E14" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="F14" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="G14" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="H14" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="H14" s="21" t="s">
+      <c r="I14" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="I14" s="38" t="s">
+      <c r="J14" s="27" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="s">
+    <row r="15" spans="1:27" ht="119">
+      <c r="A15" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="29">
-        <v>14.0</v>
-      </c>
-      <c r="D15" s="21" t="s">
+      <c r="C15" s="22">
+        <v>14</v>
+      </c>
+      <c r="D15" s="22">
+        <v>14</v>
+      </c>
+      <c r="E15" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="F15" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="G15" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="G15" s="40" t="s">
+      <c r="H15" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="H15" s="21" t="s">
+      <c r="I15" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="I15" s="38" t="s">
+      <c r="J15" s="27" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="s">
+    <row r="16" spans="1:27" ht="85">
+      <c r="A16" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C16" s="29">
-        <v>15.0</v>
-      </c>
-      <c r="D16" s="21" t="s">
+      <c r="C16" s="22">
+        <v>15</v>
+      </c>
+      <c r="D16" s="22">
+        <v>15</v>
+      </c>
+      <c r="E16" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="F16" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="G16" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="G16" s="40" t="s">
+      <c r="H16" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="H16" s="21" t="s">
+      <c r="I16" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="I16" s="39" t="s">
+      <c r="J16" s="28" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="13" t="s">
+    <row r="17" spans="1:10" ht="102">
+      <c r="A17" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="29">
-        <v>16.0</v>
-      </c>
-      <c r="D17" s="21" t="s">
+      <c r="C17" s="22">
+        <v>16</v>
+      </c>
+      <c r="D17" s="22">
+        <v>16</v>
+      </c>
+      <c r="E17" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="E17" s="30" t="s">
+      <c r="F17" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="G17" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="G17" s="30" t="s">
+      <c r="H17" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="H17" s="21" t="s">
+      <c r="I17" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="I17" s="36" t="s">
+      <c r="J17" s="27" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="13" t="s">
+    <row r="18" spans="1:10" ht="68">
+      <c r="A18" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="29">
-        <v>17.0</v>
-      </c>
-      <c r="D18" s="21" t="s">
+      <c r="C18" s="22">
+        <v>17</v>
+      </c>
+      <c r="D18" s="22">
+        <v>17</v>
+      </c>
+      <c r="E18" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="E18" s="39" t="s">
+      <c r="F18" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="G18" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="G18" s="40" t="s">
+      <c r="H18" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="H18" s="21" t="s">
+      <c r="I18" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="I18" s="39" t="s">
+      <c r="J18" s="28" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="13" t="s">
+    <row r="19" spans="1:10" ht="85">
+      <c r="A19" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="29">
-        <v>18.0</v>
-      </c>
-      <c r="D19" s="21" t="s">
+      <c r="C19" s="22">
+        <v>18</v>
+      </c>
+      <c r="D19" s="22">
+        <v>18</v>
+      </c>
+      <c r="E19" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="E19" s="37" t="s">
+      <c r="F19" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="G19" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="G19" s="40" t="s">
+      <c r="H19" s="29" t="s">
         <v>145</v>
       </c>
-      <c r="H19" s="21" t="s">
+      <c r="I19" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="I19" s="38" t="s">
+      <c r="J19" s="27" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="13" t="s">
+    <row r="20" spans="1:10" ht="102">
+      <c r="A20" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="29">
-        <v>19.0</v>
-      </c>
-      <c r="D20" s="21" t="s">
+      <c r="C20" s="22">
+        <v>19</v>
+      </c>
+      <c r="D20" s="22">
+        <v>19</v>
+      </c>
+      <c r="E20" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="E20" s="37" t="s">
+      <c r="F20" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="F20" s="21" t="s">
+      <c r="G20" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="G20" s="40" t="s">
+      <c r="H20" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="H20" s="21" t="s">
+      <c r="I20" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="I20" s="38" t="s">
+      <c r="J20" s="27" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="13" t="s">
+    <row r="21" spans="1:10" ht="102">
+      <c r="A21" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C21" s="29">
-        <v>20.0</v>
-      </c>
-      <c r="D21" s="21" t="s">
+      <c r="C21" s="22">
+        <v>20</v>
+      </c>
+      <c r="D21" s="22">
+        <v>20</v>
+      </c>
+      <c r="E21" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="E21" s="37" t="s">
+      <c r="F21" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="G21" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="G21" s="40" t="s">
+      <c r="H21" s="29" t="s">
         <v>157</v>
       </c>
-      <c r="H21" s="21" t="s">
+      <c r="I21" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="I21" s="38" t="s">
+      <c r="J21" s="27" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="13" t="s">
+    <row r="22" spans="1:10" ht="85">
+      <c r="A22" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="C22" s="29">
-        <v>21.0</v>
-      </c>
-      <c r="D22" s="21" t="s">
+      <c r="C22" s="22">
+        <v>21</v>
+      </c>
+      <c r="D22" s="22">
+        <v>21</v>
+      </c>
+      <c r="E22" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="E22" s="37" t="s">
+      <c r="F22" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="F22" s="21" t="s">
+      <c r="G22" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="G22" s="40" t="s">
+      <c r="H22" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="H22" s="21" t="s">
+      <c r="I22" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="I22" s="38" t="s">
+      <c r="J22" s="27" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="13" t="s">
+    <row r="23" spans="1:10" ht="85">
+      <c r="A23" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="C23" s="29">
-        <v>22.0</v>
-      </c>
-      <c r="D23" s="21" t="s">
+      <c r="C23" s="22">
+        <v>22</v>
+      </c>
+      <c r="D23" s="22">
+        <v>22</v>
+      </c>
+      <c r="E23" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="E23" s="37" t="s">
+      <c r="F23" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="F23" s="21" t="s">
+      <c r="G23" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="G23" s="40" t="s">
+      <c r="H23" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="H23" s="21" t="s">
+      <c r="I23" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="I23" s="39" t="s">
+      <c r="J23" s="28" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="13" t="s">
+    <row r="24" spans="1:10" ht="85">
+      <c r="A24" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="C24" s="29">
-        <v>23.0</v>
-      </c>
-      <c r="D24" s="21" t="s">
+      <c r="C24" s="22">
+        <v>23</v>
+      </c>
+      <c r="D24" s="22">
+        <v>23</v>
+      </c>
+      <c r="E24" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="E24" s="37" t="s">
+      <c r="F24" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="F24" s="21" t="s">
+      <c r="G24" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="G24" s="37" t="s">
+      <c r="H24" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="H24" s="21" t="s">
+      <c r="I24" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="I24" s="38" t="s">
+      <c r="J24" s="27" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="13" t="s">
+    <row r="25" spans="1:10" ht="68">
+      <c r="A25" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="C25" s="29">
-        <v>24.0</v>
-      </c>
-      <c r="D25" s="21" t="s">
+      <c r="C25" s="22">
+        <v>24</v>
+      </c>
+      <c r="D25" s="22">
+        <v>24</v>
+      </c>
+      <c r="E25" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="E25" s="39" t="s">
+      <c r="F25" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="F25" s="21" t="s">
+      <c r="G25" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="G25" s="40" t="s">
+      <c r="H25" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="H25" s="21" t="s">
+      <c r="I25" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="I25" s="38" t="s">
+      <c r="J25" s="27" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="13" t="s">
+    <row r="26" spans="1:10" ht="153">
+      <c r="A26" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="C26" s="29">
-        <v>25.0</v>
-      </c>
-      <c r="D26" s="21" t="s">
+      <c r="C26" s="22">
+        <v>25</v>
+      </c>
+      <c r="D26" s="22">
+        <v>25</v>
+      </c>
+      <c r="E26" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="E26" s="39" t="s">
+      <c r="F26" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="F26" s="21" t="s">
+      <c r="G26" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="G26" s="37" t="s">
+      <c r="H26" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="H26" s="21" t="s">
+      <c r="I26" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="I26" s="41" t="s">
+      <c r="J26" s="26" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="13" t="s">
+    <row r="27" spans="1:10" ht="153">
+      <c r="A27" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="C27" s="42">
-        <v>26.0</v>
-      </c>
-      <c r="D27" s="43" t="s">
+      <c r="C27" s="30">
+        <v>26</v>
+      </c>
+      <c r="D27" s="30">
+        <v>26</v>
+      </c>
+      <c r="E27" s="31" t="s">
         <v>194</v>
       </c>
-      <c r="E27" s="37" t="s">
+      <c r="F27" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="F27" s="43" t="s">
+      <c r="G27" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="G27" s="37" t="s">
+      <c r="H27" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="H27" s="43" t="s">
+      <c r="I27" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="I27" s="44" t="s">
+      <c r="J27" s="32" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="I28" s="45"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="I29" s="45"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="I30" s="45"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="I31" s="45"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="I32" s="45"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="I33" s="45"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="I34" s="45"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="I35" s="45"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="I36" s="45"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="I37" s="45"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="I38" s="45"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="I39" s="45"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="I40" s="45"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="I41" s="45"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="I42" s="45"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="I43" s="45"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="I44" s="45"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="I45" s="45"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="I46" s="45"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="I47" s="45"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="I48" s="45"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="I49" s="45"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="I50" s="45"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="I51" s="45"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="I52" s="45"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="I53" s="45"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="I54" s="45"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="I55" s="45"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="I56" s="45"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="I57" s="45"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="I58" s="45"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="I59" s="45"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="I60" s="45"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="I61" s="45"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="I62" s="45"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="I63" s="45"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="I64" s="45"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="I65" s="45"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="I66" s="45"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="I67" s="45"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="I68" s="45"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="I69" s="45"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="I70" s="45"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="I71" s="45"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="I72" s="45"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="I73" s="45"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="I74" s="45"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="I75" s="45"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="I76" s="45"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="I77" s="45"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="I78" s="45"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="I79" s="45"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="I80" s="45"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="I81" s="45"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="I82" s="45"/>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="I83" s="45"/>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="I84" s="45"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="I85" s="45"/>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="I86" s="45"/>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="I87" s="45"/>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="I88" s="45"/>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="I89" s="45"/>
-    </row>
-    <row r="90" ht="15.75" customHeight="1">
-      <c r="I90" s="45"/>
-    </row>
-    <row r="91" ht="15.75" customHeight="1">
-      <c r="I91" s="45"/>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="I92" s="45"/>
-    </row>
-    <row r="93" ht="15.75" customHeight="1">
-      <c r="I93" s="45"/>
-    </row>
-    <row r="94" ht="15.75" customHeight="1">
-      <c r="I94" s="45"/>
-    </row>
-    <row r="95" ht="15.75" customHeight="1">
-      <c r="I95" s="45"/>
-    </row>
-    <row r="96" ht="15.75" customHeight="1">
-      <c r="I96" s="45"/>
-    </row>
-    <row r="97" ht="15.75" customHeight="1">
-      <c r="I97" s="45"/>
-    </row>
-    <row r="98" ht="15.75" customHeight="1">
-      <c r="I98" s="45"/>
-    </row>
-    <row r="99" ht="15.75" customHeight="1">
-      <c r="I99" s="45"/>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="I100" s="45"/>
-    </row>
-    <row r="101" ht="15.75" customHeight="1">
-      <c r="I101" s="45"/>
-    </row>
-    <row r="102" ht="15.75" customHeight="1">
-      <c r="I102" s="45"/>
-    </row>
-    <row r="103" ht="15.75" customHeight="1">
-      <c r="I103" s="45"/>
-    </row>
-    <row r="104" ht="15.75" customHeight="1">
-      <c r="I104" s="45"/>
-    </row>
-    <row r="105" ht="15.75" customHeight="1">
-      <c r="I105" s="45"/>
-    </row>
-    <row r="106" ht="15.75" customHeight="1">
-      <c r="I106" s="45"/>
-    </row>
-    <row r="107" ht="15.75" customHeight="1">
-      <c r="I107" s="45"/>
-    </row>
-    <row r="108" ht="15.75" customHeight="1">
-      <c r="I108" s="45"/>
-    </row>
-    <row r="109" ht="15.75" customHeight="1">
-      <c r="I109" s="45"/>
-    </row>
-    <row r="110" ht="15.75" customHeight="1">
-      <c r="I110" s="45"/>
-    </row>
-    <row r="111" ht="15.75" customHeight="1">
-      <c r="I111" s="45"/>
-    </row>
-    <row r="112" ht="15.75" customHeight="1">
-      <c r="I112" s="45"/>
-    </row>
-    <row r="113" ht="15.75" customHeight="1">
-      <c r="I113" s="45"/>
-    </row>
-    <row r="114" ht="15.75" customHeight="1">
-      <c r="I114" s="45"/>
-    </row>
-    <row r="115" ht="15.75" customHeight="1">
-      <c r="I115" s="45"/>
-    </row>
-    <row r="116" ht="15.75" customHeight="1">
-      <c r="I116" s="45"/>
-    </row>
-    <row r="117" ht="15.75" customHeight="1">
-      <c r="I117" s="45"/>
-    </row>
-    <row r="118" ht="15.75" customHeight="1">
-      <c r="I118" s="45"/>
-    </row>
-    <row r="119" ht="15.75" customHeight="1">
-      <c r="I119" s="45"/>
-    </row>
-    <row r="120" ht="15.75" customHeight="1">
-      <c r="I120" s="45"/>
-    </row>
-    <row r="121" ht="15.75" customHeight="1">
-      <c r="I121" s="45"/>
-    </row>
-    <row r="122" ht="15.75" customHeight="1">
-      <c r="I122" s="45"/>
-    </row>
-    <row r="123" ht="15.75" customHeight="1">
-      <c r="I123" s="45"/>
-    </row>
-    <row r="124" ht="15.75" customHeight="1">
-      <c r="I124" s="45"/>
-    </row>
-    <row r="125" ht="15.75" customHeight="1">
-      <c r="I125" s="45"/>
-    </row>
-    <row r="126" ht="15.75" customHeight="1">
-      <c r="I126" s="45"/>
-    </row>
-    <row r="127" ht="15.75" customHeight="1">
-      <c r="I127" s="45"/>
-    </row>
-    <row r="128" ht="15.75" customHeight="1">
-      <c r="I128" s="45"/>
-    </row>
-    <row r="129" ht="15.75" customHeight="1">
-      <c r="I129" s="45"/>
-    </row>
-    <row r="130" ht="15.75" customHeight="1">
-      <c r="I130" s="45"/>
-    </row>
-    <row r="131" ht="15.75" customHeight="1">
-      <c r="I131" s="45"/>
-    </row>
-    <row r="132" ht="15.75" customHeight="1">
-      <c r="I132" s="45"/>
-    </row>
-    <row r="133" ht="15.75" customHeight="1">
-      <c r="I133" s="45"/>
-    </row>
-    <row r="134" ht="15.75" customHeight="1">
-      <c r="I134" s="45"/>
-    </row>
-    <row r="135" ht="15.75" customHeight="1">
-      <c r="I135" s="45"/>
-    </row>
-    <row r="136" ht="15.75" customHeight="1">
-      <c r="I136" s="45"/>
-    </row>
-    <row r="137" ht="15.75" customHeight="1">
-      <c r="I137" s="45"/>
-    </row>
-    <row r="138" ht="15.75" customHeight="1">
-      <c r="I138" s="45"/>
-    </row>
-    <row r="139" ht="15.75" customHeight="1">
-      <c r="I139" s="45"/>
-    </row>
-    <row r="140" ht="15.75" customHeight="1">
-      <c r="I140" s="45"/>
-    </row>
-    <row r="141" ht="15.75" customHeight="1">
-      <c r="I141" s="45"/>
-    </row>
-    <row r="142" ht="15.75" customHeight="1">
-      <c r="I142" s="45"/>
-    </row>
-    <row r="143" ht="15.75" customHeight="1">
-      <c r="I143" s="45"/>
-    </row>
-    <row r="144" ht="15.75" customHeight="1">
-      <c r="I144" s="45"/>
-    </row>
-    <row r="145" ht="15.75" customHeight="1">
-      <c r="I145" s="45"/>
-    </row>
-    <row r="146" ht="15.75" customHeight="1">
-      <c r="I146" s="45"/>
-    </row>
-    <row r="147" ht="15.75" customHeight="1">
-      <c r="I147" s="45"/>
-    </row>
-    <row r="148" ht="15.75" customHeight="1">
-      <c r="I148" s="45"/>
-    </row>
-    <row r="149" ht="15.75" customHeight="1">
-      <c r="I149" s="45"/>
-    </row>
-    <row r="150" ht="15.75" customHeight="1">
-      <c r="I150" s="45"/>
-    </row>
-    <row r="151" ht="15.75" customHeight="1">
-      <c r="I151" s="45"/>
-    </row>
-    <row r="152" ht="15.75" customHeight="1">
-      <c r="I152" s="45"/>
-    </row>
-    <row r="153" ht="15.75" customHeight="1">
-      <c r="I153" s="45"/>
-    </row>
-    <row r="154" ht="15.75" customHeight="1">
-      <c r="I154" s="45"/>
-    </row>
-    <row r="155" ht="15.75" customHeight="1">
-      <c r="I155" s="45"/>
-    </row>
-    <row r="156" ht="15.75" customHeight="1">
-      <c r="I156" s="45"/>
-    </row>
-    <row r="157" ht="15.75" customHeight="1">
-      <c r="I157" s="45"/>
-    </row>
-    <row r="158" ht="15.75" customHeight="1">
-      <c r="I158" s="45"/>
-    </row>
-    <row r="159" ht="15.75" customHeight="1">
-      <c r="I159" s="45"/>
-    </row>
-    <row r="160" ht="15.75" customHeight="1">
-      <c r="I160" s="45"/>
-    </row>
-    <row r="161" ht="15.75" customHeight="1">
-      <c r="I161" s="45"/>
-    </row>
-    <row r="162" ht="15.75" customHeight="1">
-      <c r="I162" s="45"/>
-    </row>
-    <row r="163" ht="15.75" customHeight="1">
-      <c r="I163" s="45"/>
-    </row>
-    <row r="164" ht="15.75" customHeight="1">
-      <c r="I164" s="45"/>
-    </row>
-    <row r="165" ht="15.75" customHeight="1">
-      <c r="I165" s="45"/>
-    </row>
-    <row r="166" ht="15.75" customHeight="1">
-      <c r="I166" s="45"/>
-    </row>
-    <row r="167" ht="15.75" customHeight="1">
-      <c r="I167" s="45"/>
-    </row>
-    <row r="168" ht="15.75" customHeight="1">
-      <c r="I168" s="45"/>
-    </row>
-    <row r="169" ht="15.75" customHeight="1">
-      <c r="I169" s="45"/>
-    </row>
-    <row r="170" ht="15.75" customHeight="1">
-      <c r="I170" s="45"/>
-    </row>
-    <row r="171" ht="15.75" customHeight="1">
-      <c r="I171" s="45"/>
-    </row>
-    <row r="172" ht="15.75" customHeight="1">
-      <c r="I172" s="45"/>
-    </row>
-    <row r="173" ht="15.75" customHeight="1">
-      <c r="I173" s="45"/>
-    </row>
-    <row r="174" ht="15.75" customHeight="1">
-      <c r="I174" s="45"/>
-    </row>
-    <row r="175" ht="15.75" customHeight="1">
-      <c r="I175" s="45"/>
-    </row>
-    <row r="176" ht="15.75" customHeight="1">
-      <c r="I176" s="45"/>
-    </row>
-    <row r="177" ht="15.75" customHeight="1">
-      <c r="I177" s="45"/>
-    </row>
-    <row r="178" ht="15.75" customHeight="1">
-      <c r="I178" s="45"/>
-    </row>
-    <row r="179" ht="15.75" customHeight="1">
-      <c r="I179" s="45"/>
-    </row>
-    <row r="180" ht="15.75" customHeight="1">
-      <c r="I180" s="45"/>
-    </row>
-    <row r="181" ht="15.75" customHeight="1">
-      <c r="I181" s="45"/>
-    </row>
-    <row r="182" ht="15.75" customHeight="1">
-      <c r="I182" s="45"/>
-    </row>
-    <row r="183" ht="15.75" customHeight="1">
-      <c r="I183" s="45"/>
-    </row>
-    <row r="184" ht="15.75" customHeight="1">
-      <c r="I184" s="45"/>
-    </row>
-    <row r="185" ht="15.75" customHeight="1">
-      <c r="I185" s="45"/>
-    </row>
-    <row r="186" ht="15.75" customHeight="1">
-      <c r="I186" s="45"/>
-    </row>
-    <row r="187" ht="15.75" customHeight="1">
-      <c r="I187" s="45"/>
-    </row>
-    <row r="188" ht="15.75" customHeight="1">
-      <c r="I188" s="45"/>
-    </row>
-    <row r="189" ht="15.75" customHeight="1">
-      <c r="I189" s="45"/>
-    </row>
-    <row r="190" ht="15.75" customHeight="1">
-      <c r="I190" s="45"/>
-    </row>
-    <row r="191" ht="15.75" customHeight="1">
-      <c r="I191" s="45"/>
-    </row>
-    <row r="192" ht="15.75" customHeight="1">
-      <c r="I192" s="45"/>
-    </row>
-    <row r="193" ht="15.75" customHeight="1">
-      <c r="I193" s="45"/>
-    </row>
-    <row r="194" ht="15.75" customHeight="1">
-      <c r="I194" s="45"/>
-    </row>
-    <row r="195" ht="15.75" customHeight="1">
-      <c r="I195" s="45"/>
-    </row>
-    <row r="196" ht="15.75" customHeight="1">
-      <c r="I196" s="45"/>
-    </row>
-    <row r="197" ht="15.75" customHeight="1">
-      <c r="I197" s="45"/>
-    </row>
-    <row r="198" ht="15.75" customHeight="1">
-      <c r="I198" s="45"/>
-    </row>
-    <row r="199" ht="15.75" customHeight="1">
-      <c r="I199" s="45"/>
-    </row>
-    <row r="200" ht="15.75" customHeight="1">
-      <c r="I200" s="45"/>
-    </row>
-    <row r="201" ht="15.75" customHeight="1">
-      <c r="I201" s="45"/>
-    </row>
-    <row r="202" ht="15.75" customHeight="1">
-      <c r="I202" s="45"/>
-    </row>
-    <row r="203" ht="15.75" customHeight="1">
-      <c r="I203" s="45"/>
-    </row>
-    <row r="204" ht="15.75" customHeight="1">
-      <c r="I204" s="45"/>
-    </row>
-    <row r="205" ht="15.75" customHeight="1">
-      <c r="I205" s="45"/>
-    </row>
-    <row r="206" ht="15.75" customHeight="1">
-      <c r="I206" s="45"/>
-    </row>
-    <row r="207" ht="15.75" customHeight="1">
-      <c r="I207" s="45"/>
-    </row>
-    <row r="208" ht="15.75" customHeight="1">
-      <c r="I208" s="45"/>
-    </row>
-    <row r="209" ht="15.75" customHeight="1">
-      <c r="I209" s="45"/>
-    </row>
-    <row r="210" ht="15.75" customHeight="1">
-      <c r="I210" s="45"/>
-    </row>
-    <row r="211" ht="15.75" customHeight="1">
-      <c r="I211" s="45"/>
-    </row>
-    <row r="212" ht="15.75" customHeight="1">
-      <c r="I212" s="45"/>
-    </row>
-    <row r="213" ht="15.75" customHeight="1">
-      <c r="I213" s="45"/>
-    </row>
-    <row r="214" ht="15.75" customHeight="1">
-      <c r="I214" s="45"/>
-    </row>
-    <row r="215" ht="15.75" customHeight="1">
-      <c r="I215" s="45"/>
-    </row>
-    <row r="216" ht="15.75" customHeight="1">
-      <c r="I216" s="45"/>
-    </row>
-    <row r="217" ht="15.75" customHeight="1">
-      <c r="I217" s="45"/>
-    </row>
-    <row r="218" ht="15.75" customHeight="1">
-      <c r="I218" s="45"/>
-    </row>
-    <row r="219" ht="15.75" customHeight="1">
-      <c r="I219" s="45"/>
-    </row>
-    <row r="220" ht="15.75" customHeight="1">
-      <c r="I220" s="45"/>
-    </row>
-    <row r="221" ht="15.75" customHeight="1">
-      <c r="I221" s="45"/>
-    </row>
-    <row r="222" ht="15.75" customHeight="1">
-      <c r="I222" s="45"/>
-    </row>
-    <row r="223" ht="15.75" customHeight="1">
-      <c r="I223" s="45"/>
-    </row>
-    <row r="224" ht="15.75" customHeight="1">
-      <c r="I224" s="45"/>
-    </row>
-    <row r="225" ht="15.75" customHeight="1">
-      <c r="I225" s="45"/>
-    </row>
-    <row r="226" ht="15.75" customHeight="1">
-      <c r="I226" s="45"/>
-    </row>
-    <row r="227" ht="15.75" customHeight="1">
-      <c r="I227" s="45"/>
-    </row>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:10" ht="15.75" customHeight="1">
+      <c r="J28" s="33"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" customHeight="1">
+      <c r="J29" s="33"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" customHeight="1">
+      <c r="J30" s="33"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" customHeight="1">
+      <c r="J31" s="33"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" customHeight="1">
+      <c r="J32" s="33"/>
+    </row>
+    <row r="33" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J33" s="33"/>
+    </row>
+    <row r="34" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J34" s="33"/>
+    </row>
+    <row r="35" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J35" s="33"/>
+    </row>
+    <row r="36" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J36" s="33"/>
+    </row>
+    <row r="37" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J37" s="33"/>
+    </row>
+    <row r="38" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J38" s="33"/>
+    </row>
+    <row r="39" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J39" s="33"/>
+    </row>
+    <row r="40" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J40" s="33"/>
+    </row>
+    <row r="41" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J41" s="33"/>
+    </row>
+    <row r="42" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J42" s="33"/>
+    </row>
+    <row r="43" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J43" s="33"/>
+    </row>
+    <row r="44" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J44" s="33"/>
+    </row>
+    <row r="45" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J45" s="33"/>
+    </row>
+    <row r="46" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J46" s="33"/>
+    </row>
+    <row r="47" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J47" s="33"/>
+    </row>
+    <row r="48" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J48" s="33"/>
+    </row>
+    <row r="49" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J49" s="33"/>
+    </row>
+    <row r="50" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J50" s="33"/>
+    </row>
+    <row r="51" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J51" s="33"/>
+    </row>
+    <row r="52" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J52" s="33"/>
+    </row>
+    <row r="53" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J53" s="33"/>
+    </row>
+    <row r="54" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J54" s="33"/>
+    </row>
+    <row r="55" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J55" s="33"/>
+    </row>
+    <row r="56" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J56" s="33"/>
+    </row>
+    <row r="57" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J57" s="33"/>
+    </row>
+    <row r="58" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J58" s="33"/>
+    </row>
+    <row r="59" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J59" s="33"/>
+    </row>
+    <row r="60" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J60" s="33"/>
+    </row>
+    <row r="61" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J61" s="33"/>
+    </row>
+    <row r="62" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J62" s="33"/>
+    </row>
+    <row r="63" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J63" s="33"/>
+    </row>
+    <row r="64" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J64" s="33"/>
+    </row>
+    <row r="65" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J65" s="33"/>
+    </row>
+    <row r="66" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J66" s="33"/>
+    </row>
+    <row r="67" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J67" s="33"/>
+    </row>
+    <row r="68" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J68" s="33"/>
+    </row>
+    <row r="69" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J69" s="33"/>
+    </row>
+    <row r="70" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J70" s="33"/>
+    </row>
+    <row r="71" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J71" s="33"/>
+    </row>
+    <row r="72" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J72" s="33"/>
+    </row>
+    <row r="73" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J73" s="33"/>
+    </row>
+    <row r="74" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J74" s="33"/>
+    </row>
+    <row r="75" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J75" s="33"/>
+    </row>
+    <row r="76" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J76" s="33"/>
+    </row>
+    <row r="77" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J77" s="33"/>
+    </row>
+    <row r="78" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J78" s="33"/>
+    </row>
+    <row r="79" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J79" s="33"/>
+    </row>
+    <row r="80" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J80" s="33"/>
+    </row>
+    <row r="81" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J81" s="33"/>
+    </row>
+    <row r="82" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J82" s="33"/>
+    </row>
+    <row r="83" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J83" s="33"/>
+    </row>
+    <row r="84" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J84" s="33"/>
+    </row>
+    <row r="85" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J85" s="33"/>
+    </row>
+    <row r="86" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J86" s="33"/>
+    </row>
+    <row r="87" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J87" s="33"/>
+    </row>
+    <row r="88" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J88" s="33"/>
+    </row>
+    <row r="89" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J89" s="33"/>
+    </row>
+    <row r="90" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J90" s="33"/>
+    </row>
+    <row r="91" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J91" s="33"/>
+    </row>
+    <row r="92" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J92" s="33"/>
+    </row>
+    <row r="93" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J93" s="33"/>
+    </row>
+    <row r="94" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J94" s="33"/>
+    </row>
+    <row r="95" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J95" s="33"/>
+    </row>
+    <row r="96" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J96" s="33"/>
+    </row>
+    <row r="97" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J97" s="33"/>
+    </row>
+    <row r="98" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J98" s="33"/>
+    </row>
+    <row r="99" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J99" s="33"/>
+    </row>
+    <row r="100" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J100" s="33"/>
+    </row>
+    <row r="101" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J101" s="33"/>
+    </row>
+    <row r="102" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J102" s="33"/>
+    </row>
+    <row r="103" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J103" s="33"/>
+    </row>
+    <row r="104" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J104" s="33"/>
+    </row>
+    <row r="105" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J105" s="33"/>
+    </row>
+    <row r="106" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J106" s="33"/>
+    </row>
+    <row r="107" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J107" s="33"/>
+    </row>
+    <row r="108" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J108" s="33"/>
+    </row>
+    <row r="109" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J109" s="33"/>
+    </row>
+    <row r="110" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J110" s="33"/>
+    </row>
+    <row r="111" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J111" s="33"/>
+    </row>
+    <row r="112" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J112" s="33"/>
+    </row>
+    <row r="113" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J113" s="33"/>
+    </row>
+    <row r="114" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J114" s="33"/>
+    </row>
+    <row r="115" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J115" s="33"/>
+    </row>
+    <row r="116" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J116" s="33"/>
+    </row>
+    <row r="117" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J117" s="33"/>
+    </row>
+    <row r="118" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J118" s="33"/>
+    </row>
+    <row r="119" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J119" s="33"/>
+    </row>
+    <row r="120" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J120" s="33"/>
+    </row>
+    <row r="121" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J121" s="33"/>
+    </row>
+    <row r="122" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J122" s="33"/>
+    </row>
+    <row r="123" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J123" s="33"/>
+    </row>
+    <row r="124" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J124" s="33"/>
+    </row>
+    <row r="125" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J125" s="33"/>
+    </row>
+    <row r="126" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J126" s="33"/>
+    </row>
+    <row r="127" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J127" s="33"/>
+    </row>
+    <row r="128" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J128" s="33"/>
+    </row>
+    <row r="129" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J129" s="33"/>
+    </row>
+    <row r="130" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J130" s="33"/>
+    </row>
+    <row r="131" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J131" s="33"/>
+    </row>
+    <row r="132" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J132" s="33"/>
+    </row>
+    <row r="133" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J133" s="33"/>
+    </row>
+    <row r="134" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J134" s="33"/>
+    </row>
+    <row r="135" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J135" s="33"/>
+    </row>
+    <row r="136" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J136" s="33"/>
+    </row>
+    <row r="137" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J137" s="33"/>
+    </row>
+    <row r="138" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J138" s="33"/>
+    </row>
+    <row r="139" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J139" s="33"/>
+    </row>
+    <row r="140" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J140" s="33"/>
+    </row>
+    <row r="141" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J141" s="33"/>
+    </row>
+    <row r="142" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J142" s="33"/>
+    </row>
+    <row r="143" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J143" s="33"/>
+    </row>
+    <row r="144" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J144" s="33"/>
+    </row>
+    <row r="145" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J145" s="33"/>
+    </row>
+    <row r="146" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J146" s="33"/>
+    </row>
+    <row r="147" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J147" s="33"/>
+    </row>
+    <row r="148" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J148" s="33"/>
+    </row>
+    <row r="149" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J149" s="33"/>
+    </row>
+    <row r="150" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J150" s="33"/>
+    </row>
+    <row r="151" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J151" s="33"/>
+    </row>
+    <row r="152" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J152" s="33"/>
+    </row>
+    <row r="153" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J153" s="33"/>
+    </row>
+    <row r="154" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J154" s="33"/>
+    </row>
+    <row r="155" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J155" s="33"/>
+    </row>
+    <row r="156" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J156" s="33"/>
+    </row>
+    <row r="157" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J157" s="33"/>
+    </row>
+    <row r="158" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J158" s="33"/>
+    </row>
+    <row r="159" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J159" s="33"/>
+    </row>
+    <row r="160" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J160" s="33"/>
+    </row>
+    <row r="161" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J161" s="33"/>
+    </row>
+    <row r="162" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J162" s="33"/>
+    </row>
+    <row r="163" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J163" s="33"/>
+    </row>
+    <row r="164" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J164" s="33"/>
+    </row>
+    <row r="165" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J165" s="33"/>
+    </row>
+    <row r="166" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J166" s="33"/>
+    </row>
+    <row r="167" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J167" s="33"/>
+    </row>
+    <row r="168" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J168" s="33"/>
+    </row>
+    <row r="169" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J169" s="33"/>
+    </row>
+    <row r="170" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J170" s="33"/>
+    </row>
+    <row r="171" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J171" s="33"/>
+    </row>
+    <row r="172" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J172" s="33"/>
+    </row>
+    <row r="173" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J173" s="33"/>
+    </row>
+    <row r="174" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J174" s="33"/>
+    </row>
+    <row r="175" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J175" s="33"/>
+    </row>
+    <row r="176" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J176" s="33"/>
+    </row>
+    <row r="177" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J177" s="33"/>
+    </row>
+    <row r="178" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J178" s="33"/>
+    </row>
+    <row r="179" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J179" s="33"/>
+    </row>
+    <row r="180" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J180" s="33"/>
+    </row>
+    <row r="181" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J181" s="33"/>
+    </row>
+    <row r="182" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J182" s="33"/>
+    </row>
+    <row r="183" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J183" s="33"/>
+    </row>
+    <row r="184" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J184" s="33"/>
+    </row>
+    <row r="185" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J185" s="33"/>
+    </row>
+    <row r="186" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J186" s="33"/>
+    </row>
+    <row r="187" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J187" s="33"/>
+    </row>
+    <row r="188" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J188" s="33"/>
+    </row>
+    <row r="189" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J189" s="33"/>
+    </row>
+    <row r="190" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J190" s="33"/>
+    </row>
+    <row r="191" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J191" s="33"/>
+    </row>
+    <row r="192" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J192" s="33"/>
+    </row>
+    <row r="193" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J193" s="33"/>
+    </row>
+    <row r="194" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J194" s="33"/>
+    </row>
+    <row r="195" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J195" s="33"/>
+    </row>
+    <row r="196" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J196" s="33"/>
+    </row>
+    <row r="197" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J197" s="33"/>
+    </row>
+    <row r="198" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J198" s="33"/>
+    </row>
+    <row r="199" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J199" s="33"/>
+    </row>
+    <row r="200" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J200" s="33"/>
+    </row>
+    <row r="201" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J201" s="33"/>
+    </row>
+    <row r="202" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J202" s="33"/>
+    </row>
+    <row r="203" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J203" s="33"/>
+    </row>
+    <row r="204" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J204" s="33"/>
+    </row>
+    <row r="205" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J205" s="33"/>
+    </row>
+    <row r="206" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J206" s="33"/>
+    </row>
+    <row r="207" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J207" s="33"/>
+    </row>
+    <row r="208" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J208" s="33"/>
+    </row>
+    <row r="209" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J209" s="33"/>
+    </row>
+    <row r="210" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J210" s="33"/>
+    </row>
+    <row r="211" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J211" s="33"/>
+    </row>
+    <row r="212" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J212" s="33"/>
+    </row>
+    <row r="213" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J213" s="33"/>
+    </row>
+    <row r="214" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J214" s="33"/>
+    </row>
+    <row r="215" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J215" s="33"/>
+    </row>
+    <row r="216" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J216" s="33"/>
+    </row>
+    <row r="217" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J217" s="33"/>
+    </row>
+    <row r="218" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J218" s="33"/>
+    </row>
+    <row r="219" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J219" s="33"/>
+    </row>
+    <row r="220" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J220" s="33"/>
+    </row>
+    <row r="221" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J221" s="33"/>
+    </row>
+    <row r="222" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J222" s="33"/>
+    </row>
+    <row r="223" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J223" s="33"/>
+    </row>
+    <row r="224" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J224" s="33"/>
+    </row>
+    <row r="225" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J225" s="33"/>
+    </row>
+    <row r="226" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J226" s="33"/>
+    </row>
+    <row r="227" spans="10:10" ht="15.75" customHeight="1">
+      <c r="J227" s="33"/>
+    </row>
+    <row r="228" spans="10:10" ht="15.75" customHeight="1"/>
+    <row r="229" spans="10:10" ht="15.75" customHeight="1"/>
+    <row r="230" spans="10:10" ht="15.75" customHeight="1"/>
+    <row r="231" spans="10:10" ht="15.75" customHeight="1"/>
+    <row r="232" spans="10:10" ht="15.75" customHeight="1"/>
+    <row r="233" spans="10:10" ht="15.75" customHeight="1"/>
+    <row r="234" spans="10:10" ht="15.75" customHeight="1"/>
+    <row r="235" spans="10:10" ht="15.75" customHeight="1"/>
+    <row r="236" spans="10:10" ht="15.75" customHeight="1"/>
+    <row r="237" spans="10:10" ht="15.75" customHeight="1"/>
+    <row r="238" spans="10:10" ht="15.75" customHeight="1"/>
+    <row r="239" spans="10:10" ht="15.75" customHeight="1"/>
+    <row r="240" spans="10:10" ht="15.75" customHeight="1"/>
     <row r="241" ht="15.75" customHeight="1"/>
     <row r="242" ht="15.75" customHeight="1"/>
     <row r="243" ht="15.75" customHeight="1"/>
@@ -10722,84 +10886,87 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B1001"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="25.0"/>
-    <col customWidth="1" min="2" max="2" width="33.0"/>
-    <col customWidth="1" min="3" max="6" width="8.22"/>
-    <col customWidth="1" min="7" max="26" width="8.56"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="33" customWidth="1"/>
+    <col min="3" max="6" width="8.1640625" customWidth="1"/>
+    <col min="7" max="26" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A1" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="46" t="s">
+    <row r="2" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A2" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="B2" s="39" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="126">
+      <c r="A3" s="34" t="s">
         <v>201</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B3" s="35" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="46" t="s">
+    <row r="4" spans="1:2" ht="84">
+      <c r="A4" s="34" t="s">
         <v>203</v>
       </c>
-      <c r="B3" s="48" t="s">
+      <c r="B4" s="36" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="46" t="s">
+    <row r="5" spans="1:2" ht="105">
+      <c r="A5" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="47" t="s">
+      <c r="B5" s="35" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="46" t="s">
+    <row r="6" spans="1:2" ht="105">
+      <c r="A6" s="34" t="s">
         <v>207</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="B6" s="35" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="46" t="s">
+    <row r="7" spans="1:2" ht="105">
+      <c r="A7" s="34" t="s">
         <v>209</v>
       </c>
-      <c r="B6" s="49" t="s">
+      <c r="B7" s="36" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1"/>
-    <row r="8" ht="15.75" customHeight="1"/>
-    <row r="9" ht="15.75" customHeight="1"/>
-    <row r="10" ht="15.75" customHeight="1"/>
-    <row r="11" ht="15.75" customHeight="1"/>
-    <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13" ht="15.75" customHeight="1"/>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="8" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="9" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="10" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="11" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="12" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="13" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="14" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="15" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="16" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
@@ -11784,10 +11951,48 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.787401575" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.787401575"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C032C56-1CFE-DD4C-A48D-CBB8BF6ECD99}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="24.5" style="37" customWidth="1"/>
+    <col min="2" max="2" width="27.1640625" style="37" customWidth="1"/>
+    <col min="3" max="16384" width="11" style="37"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>216</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/assets/translations/Spanish.Spain.es-ES.xlsx
+++ b/assets/translations/Spanish.Spain.es-ES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E3CF1D-EAB5-0A44-A3AA-00C20B235501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9468CAD-EED7-0240-B0D2-BA31358EB2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="620" windowWidth="51200" windowHeight="28180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1300" yWindow="620" windowWidth="49900" windowHeight="28180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contributors" sheetId="1" r:id="rId1"/>
@@ -167,9 +167,6 @@
     <t>The pattern of one's light exposure across the day and the year can be quite complex, and depends on where one is and what one does.</t>
   </si>
   <si>
-    <t>Establecer el patrón de exposición a la luz durante un día o un año año puede ser una tarea compleja, y depende de la localización geográfica y de la actividad diaria.</t>
-  </si>
-  <si>
     <t>The amount of light around us (or the amount we are exposed to) changes as we move between indoor and outdoor spaces, throughout the day, and across seasons.</t>
   </si>
   <si>
@@ -239,59 +236,18 @@
     <t>The properties of daylight (spectrum, intensity and spatial distribution) vary throughout the day and the year, and with changing weather.</t>
   </si>
   <si>
-    <t>Las propiedades de la luz diurna (espectro, intensidad y distribución espacial) varía a lo largo del día y del año y con los cambios meteorológicos</t>
-  </si>
-  <si>
     <t>The colour, intensity, and pattern of daylight change throughout the day, with seasons, and weather.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF70AD47"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">El color, la intensidad y el patrón de la luz diurna cambia a lo largo del día, con las estaciones </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF741B47"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>del año</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF70AD47"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> y el tiempo atmosférico.</t>
-    </r>
-  </si>
-  <si>
     <t>As sunlight travels through the atmosphere, blue light is scattered more than other wavelengths. This makes the sky appear blue.</t>
   </si>
   <si>
-    <t>A medida que la luz solar atraviesa la atmósfera, la luz azul se dispersa más que otras longitudes de onda. Esto es lo que hace que el cielo se vea azul</t>
-  </si>
-  <si>
     <t>Human photoreceptors (7-9)</t>
   </si>
   <si>
-    <t>Fotoreceptores humanos</t>
-  </si>
-  <si>
     <t>The human eye contains the retina, which has several photosensitive cells that differ in their responses to different wavelengths.</t>
   </si>
   <si>
-    <t>La retina está ubicada en el ojo humano que tiene varias células fotosensibles que difieren en su respuesta a diferentes longitudes de onda</t>
-  </si>
-  <si>
     <t>In the eye, the retina contains cells, that allow us to detect different colours (of the visible spectrum).</t>
   </si>
   <si>
@@ -325,9 +281,6 @@
     <t>The rods allow us to see rudimentary spatial detail under dim light.</t>
   </si>
   <si>
-    <t>Los bastones nos permiten ver de manera rudiemntaria los detalles espaciales con luz ténue</t>
-  </si>
-  <si>
     <t>Rod cells help us see shapes and details in dim light.</t>
   </si>
   <si>
@@ -349,9 +302,6 @@
     <t>The intrinsically photosensitive retinal ganglion cells (ipRGCs) convert light into signals that influence many physiological functions.</t>
   </si>
   <si>
-    <t>Las células ganglionares retinianas intrínsecamente fotosensibles convierten la luz en señales que influyen en muchas funciones fisiológicas</t>
-  </si>
-  <si>
     <t>When ipRGCs detect light, they send signals to the brain to regulate various bodily functions.</t>
   </si>
   <si>
@@ -391,35 +341,6 @@
     <t>Light is the primary signal that synchronizes the body's internal clock with the sun’s day-night cycle.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF70AD46"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">La luz es la principal señal que sincroniza el reloj interno del cuerpo con el ciclo diurno-nocturno </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF741B47"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>(día-noche)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF70AD46"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> del sol.</t>
-    </r>
-  </si>
-  <si>
     <t>Light helps regulate the body's internal rhythms. This ensures biological processes start and stop at appropriate times.</t>
   </si>
   <si>
@@ -447,9 +368,6 @@
     <t>Light in the morning can advance the circadian clock, and light in the evening can delay the circadian clock.</t>
   </si>
   <si>
-    <t>Luz en la mañana puede adelantar el reloj circadiano, y luz a la tarde puede retrasarlo.</t>
-  </si>
-  <si>
     <t>Morning light promotes earlier bedtime and wake time, while evening light can delay bedtime and waking.</t>
   </si>
   <si>
@@ -459,9 +377,6 @@
     <t>Light tells the brain to become active. Light in the morning advances the body’s internal clock (shifts it to an earlier “time”), while light in the evening delays it (shifts it to a later “time”).</t>
   </si>
   <si>
-    <t>La luz le indica al cerebro que se active. La luz de la mañana adelanta el reloj interno del cuerpo (lo adelanta a una «hora» más temprana), mientras que la luz de la tarde lo retrasa (lo retrasa a una «hora» más tardía).</t>
-  </si>
-  <si>
     <t>Light can also boost alertness and cognitive function under some conditions.</t>
   </si>
   <si>
@@ -513,35 +428,6 @@
     <t>Evening light exposure tells the body it is still daytime. This increases alertness and shifts the internal clock to a later time.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF00FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">La exposición a la luz </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1C4587"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">en horario nocturno </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF00FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>le indica al cuerpo que aún es de día. Esto aumenta el estado de alerta y retrasa el reloj interno.</t>
-    </r>
-  </si>
-  <si>
     <t>Higher light levels during the daytime can improve mood.</t>
   </si>
   <si>
@@ -557,26 +443,6 @@
     <t>Exposure to natural daylight (the sun) or high-intensity electric light, when free from glare, can reduce stress and improve emotional balance.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF70AD46"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Exponerse a la luz natural (el sol) o a luz eléctrica de alta intensidad, puede reducir el estrés y mejorar el equilibrio emocional, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF1C4587"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>siempre que se evite el deslumbramiento.</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">Higher light levels during the daytime can improve sleep quality in the following night. </t>
   </si>
   <si>
@@ -598,9 +464,6 @@
     <t>Following a medically-prescribed protocol for bright light, exposure in the morning can lead to improvements in mood for people with certain clinical diagnoses.</t>
   </si>
   <si>
-    <t>Seguir un protocolo médico prescrito sobre la luz brillante, la exposición por la mañana puede conducir a mejoras en el estado de ánimo de las personas con ciertos diagnósticos clínicos.</t>
-  </si>
-  <si>
     <t>Doctors may prescribe light therapy as treatment for winter depression and other health conditions.</t>
   </si>
   <si>
@@ -622,9 +485,6 @@
     <t>A healthy pattern of daily light exposure includes a rhythm of bright light and darkness every day.</t>
   </si>
   <si>
-    <t>Un patrón saludable de exposición diaria a la luz incluye un ritmo de luz brillante y oscuridad todos los días.</t>
-  </si>
-  <si>
     <t>A healthy daily routine includes bright light during the day and darkness at night.</t>
   </si>
   <si>
@@ -652,53 +512,6 @@
     <t>With age, the eye’s lenses become less transparent, which may reduce the body’s response to light exposure.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF00FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Con la edad, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF70AD46"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>el cristalino</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF00FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> de los ojos se vuelve menos transparentes, lo que puede reducir la respuesta </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF70AD46"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">del </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF00FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>cuerpo a la exposición a la luz.</t>
-    </r>
-  </si>
-  <si>
     <t>There are substantial individual differences in the physiological response to light.</t>
   </si>
   <si>
@@ -736,35 +549,6 @@
   </si>
   <si>
     <t>Studies investigating light exposure in the real-world are needed.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF70AD46"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Se necesitan estudios que investiguen la exposici</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF741B47"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>ón</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF70AD46"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> a la luz en el mundo real.</t>
-    </r>
   </si>
   <si>
     <t>There is a need for studies on the physiological effects of light incorporating a broad range of study populations.</t>
@@ -920,12 +704,63 @@
   <si>
     <t>Número</t>
   </si>
+  <si>
+    <t>Fotorreceptores humanos</t>
+  </si>
+  <si>
+    <t>Establecer el patrón de exposición a la luz durante un día o un año puede ser una tarea compleja, y depende de la localización geográfica y de la actividad diaria.</t>
+  </si>
+  <si>
+    <t>Las propiedades de la luz diurna (espectro, intensidad y distribución espacial) varían a lo largo del día y del año y con los cambios meteorológicos</t>
+  </si>
+  <si>
+    <t>La retina está ubicada en el interior del ojo humano; allí se localizan las células fotosensibles, que difieren en su respuesta a diferentes longitudes de onda</t>
+  </si>
+  <si>
+    <t>Los bastones nos permiten ver de manera rudimentaria los detalles espaciales bajo condiciones de luz tenue</t>
+  </si>
+  <si>
+    <t>Las células ganglionares retinianas intrínsecamente fotosensibles convierten la luz en señales que influyen en varias funciones fisiológicas</t>
+  </si>
+  <si>
+    <t>La luz en la mañana puede adelantar el reloj circadiano, y la luz en horario nocturno puede retrasarlo.</t>
+  </si>
+  <si>
+    <t>Siguiendo un protocolo médico sobre la luz brillante, la exposición por la mañana puede conducir a mejoras en el estado de ánimo de las personas con ciertos diagnósticos clínicos.</t>
+  </si>
+  <si>
+    <t>Un patrón saludable de exposición diaria a la luz incluye un ritmo alterno de luz brillante y oscuridad todos los días.</t>
+  </si>
+  <si>
+    <t>La luz es la principal señal que sincroniza el reloj interno del cuerpo con el ciclo diurno-nocturno (día-noche) del sol.</t>
+  </si>
+  <si>
+    <t>A medida que la luz solar atraviesa la atmósfera, la luz azul se dispersa más que otras longitudes de onda. Esto es lo que hace que el cielo se vea azul.</t>
+  </si>
+  <si>
+    <t>La luz le indica al cerebro que se active. La luz de la mañana adelanta el reloj interno del cuerpo (lo adelanta a una «hora» más temprana), mientras que la exposición a la luz en horario nocturno lo retrasa (lo retrasa a una «hora» más tardía).</t>
+  </si>
+  <si>
+    <t>La exposición a la luz en horario nocturno le indica al cuerpo que aún es de día. Esto aumenta el estado de alerta y retrasa el reloj interno.</t>
+  </si>
+  <si>
+    <t>Exponerse a la luz natural (el sol) o a luz eléctrica de alta intensidad, puede reducir el estrés y mejorar el equilibrio emocional, siempre que se evite el deslumbramiento.</t>
+  </si>
+  <si>
+    <t>Con la edad, el cristalino de los ojos se vuelve menos transparentes, lo que puede reducir la respuesta del cuerpo a la exposición a la luz.</t>
+  </si>
+  <si>
+    <t>Se necesitan estudios que investiguen la exposición a la luz en el mundo real.</t>
+  </si>
+  <si>
+    <t>El color, la intensidad y el patrón de la luz diurna cambia a lo largo del día, con las estaciones del año y el tiempo atmosférico.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+  <fonts count="26">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -1016,43 +851,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF741B47"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF242424"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF70AD46"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF70AD47"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF00FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="15"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -1075,18 +873,6 @@
       <sz val="12"/>
       <color rgb="FF70AD46"/>
       <name val="Calibri, sans-serif"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF741B47"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF1C4587"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1114,6 +900,28 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1289,7 +1097,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1303,88 +1111,74 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -8624,1493 +8418,1493 @@
   <dimension ref="A1:AA1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="38.6640625" customWidth="1"/>
-    <col min="2" max="2" width="19.5" customWidth="1"/>
-    <col min="3" max="4" width="7.83203125" customWidth="1"/>
-    <col min="5" max="10" width="32.83203125" customWidth="1"/>
+    <col min="1" max="1" width="38.6640625" style="35" customWidth="1"/>
+    <col min="2" max="2" width="19.5" style="35" customWidth="1"/>
+    <col min="3" max="4" width="7.83203125" style="35" customWidth="1"/>
+    <col min="5" max="10" width="32.83203125" style="35" customWidth="1"/>
     <col min="11" max="27" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="283.5" customHeight="1">
+      <c r="A2" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="25">
+        <v>1</v>
+      </c>
+      <c r="D2" s="25">
+        <v>1</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="12"/>
+      <c r="T2" s="12"/>
+      <c r="U2" s="12"/>
+      <c r="V2" s="12"/>
+      <c r="W2" s="12"/>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="12"/>
+      <c r="Z2" s="12"/>
+      <c r="AA2" s="12"/>
+    </row>
+    <row r="3" spans="1:27" ht="136">
+      <c r="A3" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="25">
+        <v>2</v>
+      </c>
+      <c r="D3" s="25">
+        <v>2</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="187">
+      <c r="A4" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="25">
+        <v>3</v>
+      </c>
+      <c r="D4" s="25">
+        <v>3</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="136">
+      <c r="A5" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="30">
+        <v>4</v>
+      </c>
+      <c r="D5" s="30">
+        <v>4</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="170">
+      <c r="A6" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="30">
+        <v>5</v>
+      </c>
+      <c r="D6" s="30">
+        <v>5</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="85">
+      <c r="A7" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="30">
+        <v>6</v>
+      </c>
+      <c r="D7" s="30">
+        <v>6</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="I7" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="31" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="136">
+      <c r="A8" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="C8" s="30">
+        <v>7</v>
+      </c>
+      <c r="D8" s="30">
+        <v>7</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="102">
+      <c r="A9" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="C9" s="30">
+        <v>8</v>
+      </c>
+      <c r="D9" s="30">
+        <v>8</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="I9" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="68">
+      <c r="A10" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="C10" s="30">
+        <v>9</v>
+      </c>
+      <c r="D10" s="30">
+        <v>9</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="85">
+      <c r="A11" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="30">
+        <v>10</v>
+      </c>
+      <c r="D11" s="30">
+        <v>10</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="136">
+      <c r="A12" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="30">
+        <v>11</v>
+      </c>
+      <c r="D12" s="30">
+        <v>11</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="G12" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="H12" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="I12" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="31" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="85">
+      <c r="A13" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="30">
+        <v>12</v>
+      </c>
+      <c r="D13" s="30">
+        <v>12</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="H13" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="I13" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="68">
+      <c r="A14" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="30">
+        <v>13</v>
+      </c>
+      <c r="D14" s="30">
+        <v>13</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="G14" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="H14" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="I14" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="J14" s="31" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="136">
+      <c r="A15" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="30">
+        <v>14</v>
+      </c>
+      <c r="D15" s="30">
+        <v>14</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>211</v>
+      </c>
+      <c r="G15" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="H15" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="I15" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="J15" s="31" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="85">
+      <c r="A16" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="30">
+        <v>15</v>
+      </c>
+      <c r="D16" s="30">
+        <v>15</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="G16" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="H16" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="J16" s="28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="102">
+      <c r="A17" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="30">
+        <v>16</v>
+      </c>
+      <c r="D17" s="30">
+        <v>16</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="G17" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="I17" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="J17" s="31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="68">
+      <c r="A18" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="30">
+        <v>17</v>
+      </c>
+      <c r="D18" s="30">
+        <v>17</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="H18" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="I18" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="J18" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="39" t="s">
-        <v>221</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="39" t="s">
+    </row>
+    <row r="19" spans="1:10" ht="85">
+      <c r="A19" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19" s="30">
+        <v>18</v>
+      </c>
+      <c r="D19" s="30">
+        <v>18</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="G19" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="H19" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="I19" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="J19" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="G1" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="39" t="s">
+    </row>
+    <row r="20" spans="1:10" ht="102">
+      <c r="A20" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="30">
+        <v>19</v>
+      </c>
+      <c r="D20" s="30">
+        <v>19</v>
+      </c>
+      <c r="E20" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="G20" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="H20" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="I20" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="J20" s="31" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="102">
+      <c r="A21" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="30">
+        <v>20</v>
+      </c>
+      <c r="D21" s="30">
+        <v>20</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21" s="27" t="s">
+        <v>212</v>
+      </c>
+      <c r="G21" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="H21" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="I21" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="J21" s="31" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="85">
+      <c r="A22" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="30">
+        <v>21</v>
+      </c>
+      <c r="D22" s="30">
+        <v>21</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="G22" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="H22" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="I22" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="J22" s="31" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="85">
+      <c r="A23" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C23" s="30">
+        <v>22</v>
+      </c>
+      <c r="D23" s="30">
+        <v>22</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="F23" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="G23" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="H23" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="I23" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="J23" s="28" t="s">
         <v>219</v>
       </c>
-      <c r="I1" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="39" t="s">
+    </row>
+    <row r="24" spans="1:10" ht="85">
+      <c r="A24" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C24" s="30">
+        <v>23</v>
+      </c>
+      <c r="D24" s="30">
+        <v>23</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="F24" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="G24" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="H24" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="J24" s="31" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="68">
+      <c r="A25" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" s="30">
+        <v>24</v>
+      </c>
+      <c r="D25" s="30">
+        <v>24</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="H25" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="I25" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="J25" s="31" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="283.5" customHeight="1">
-      <c r="A2" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="16">
-        <v>1</v>
-      </c>
-      <c r="D2" s="16">
-        <v>1</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
-      <c r="R2" s="20"/>
-      <c r="S2" s="20"/>
-      <c r="T2" s="20"/>
-      <c r="U2" s="20"/>
-      <c r="V2" s="20"/>
-      <c r="W2" s="20"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="20"/>
-      <c r="Z2" s="20"/>
-      <c r="AA2" s="20"/>
-    </row>
-    <row r="3" spans="1:27" ht="136">
-      <c r="A3" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="16">
-        <v>2</v>
-      </c>
-      <c r="D3" s="16">
-        <v>2</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="187">
-      <c r="A4" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="16">
-        <v>3</v>
-      </c>
-      <c r="D4" s="16">
-        <v>3</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="J4" s="21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="136">
-      <c r="A5" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="22">
-        <v>4</v>
-      </c>
-      <c r="D5" s="22">
-        <v>4</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="J5" s="19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="170">
-      <c r="A6" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="22">
-        <v>5</v>
-      </c>
-      <c r="D6" s="22">
-        <v>5</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="85">
-      <c r="A7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="22">
-        <v>6</v>
-      </c>
-      <c r="D7" s="22">
-        <v>6</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="H7" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="J7" s="25" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="136">
-      <c r="A8" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="22">
-        <v>7</v>
-      </c>
-      <c r="D8" s="22">
-        <v>7</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="H8" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="J8" s="25" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="102">
-      <c r="A9" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="22">
-        <v>8</v>
-      </c>
-      <c r="D9" s="22">
-        <v>8</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="J9" s="25" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="51">
-      <c r="A10" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="22">
-        <v>9</v>
-      </c>
-      <c r="D10" s="22">
-        <v>9</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="J10" s="26" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="85">
-      <c r="A11" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="22">
-        <v>10</v>
-      </c>
-      <c r="D11" s="22">
-        <v>10</v>
-      </c>
-      <c r="E11" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="G11" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="H11" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="J11" s="27" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="136">
-      <c r="A12" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="22">
-        <v>11</v>
-      </c>
-      <c r="D12" s="22">
-        <v>11</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="H12" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="J12" s="27" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="85">
-      <c r="A13" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="22">
-        <v>12</v>
-      </c>
-      <c r="D13" s="22">
-        <v>12</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>107</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="H13" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="J13" s="28" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="68">
-      <c r="A14" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="22">
-        <v>13</v>
-      </c>
-      <c r="D14" s="22">
-        <v>13</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="H14" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="J14" s="27" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="119">
-      <c r="A15" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="22">
-        <v>14</v>
-      </c>
-      <c r="D15" s="22">
-        <v>14</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>119</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="H15" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="J15" s="27" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="85">
-      <c r="A16" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="22">
-        <v>15</v>
-      </c>
-      <c r="D16" s="22">
-        <v>15</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="H16" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="I16" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="J16" s="28" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="102">
-      <c r="A17" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="22">
-        <v>16</v>
-      </c>
-      <c r="D17" s="22">
-        <v>16</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="H17" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="I17" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="J17" s="27" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="68">
-      <c r="A18" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="22">
-        <v>17</v>
-      </c>
-      <c r="D18" s="22">
-        <v>17</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="F18" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="H18" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="J18" s="28" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="85">
-      <c r="A19" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="22">
-        <v>18</v>
-      </c>
-      <c r="D19" s="22">
-        <v>18</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="G19" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="H19" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="J19" s="27" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="102">
-      <c r="A20" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" s="22">
-        <v>19</v>
-      </c>
-      <c r="D20" s="22">
-        <v>19</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="F20" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="H20" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="J20" s="27" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="102">
-      <c r="A21" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="22">
-        <v>20</v>
-      </c>
-      <c r="D21" s="22">
-        <v>20</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="H21" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="J21" s="27" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="85">
-      <c r="A22" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="C22" s="22">
-        <v>21</v>
-      </c>
-      <c r="D22" s="22">
-        <v>21</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="F22" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="G22" s="17" t="s">
+    <row r="26" spans="1:10" ht="153">
+      <c r="A26" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="H22" s="29" t="s">
+      <c r="B26" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="I22" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="J22" s="27" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="85">
-      <c r="A23" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="C23" s="22">
-        <v>22</v>
-      </c>
-      <c r="D23" s="22">
-        <v>22</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="H23" s="29" t="s">
+      <c r="C26" s="30">
+        <v>25</v>
+      </c>
+      <c r="D26" s="30">
+        <v>25</v>
+      </c>
+      <c r="E26" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="I23" s="17" t="s">
+      <c r="F26" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="J23" s="28" t="s">
+      <c r="G26" s="26" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="85">
-      <c r="A24" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="C24" s="22">
-        <v>23</v>
-      </c>
-      <c r="D24" s="22">
-        <v>23</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="H26" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="F24" s="23" t="s">
+      <c r="I26" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="G24" s="17" t="s">
+      <c r="J26" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="H24" s="23" t="s">
+    </row>
+    <row r="27" spans="1:10" ht="153">
+      <c r="A27" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" s="32">
+        <v>26</v>
+      </c>
+      <c r="D27" s="32">
+        <v>26</v>
+      </c>
+      <c r="E27" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="I24" s="17" t="s">
+      <c r="F27" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="J24" s="27" t="s">
+      <c r="G27" s="33" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="68">
-      <c r="A25" s="11" t="s">
+      <c r="H27" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="I27" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="C25" s="22">
-        <v>24</v>
-      </c>
-      <c r="D25" s="22">
-        <v>24</v>
-      </c>
-      <c r="E25" s="17" t="s">
+      <c r="J27" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="F25" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="H25" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="I25" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="J25" s="27" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="153">
-      <c r="A26" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="C26" s="22">
-        <v>25</v>
-      </c>
-      <c r="D26" s="22">
-        <v>25</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="F26" s="28" t="s">
-        <v>189</v>
-      </c>
-      <c r="G26" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="H26" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="I26" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="J26" s="26" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="153">
-      <c r="A27" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="C27" s="30">
-        <v>26</v>
-      </c>
-      <c r="D27" s="30">
-        <v>26</v>
-      </c>
-      <c r="E27" s="31" t="s">
-        <v>194</v>
-      </c>
-      <c r="F27" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="G27" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="H27" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="I27" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="J27" s="32" t="s">
-        <v>199</v>
-      </c>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1">
-      <c r="J28" s="33"/>
+      <c r="J28" s="36"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1">
-      <c r="J29" s="33"/>
+      <c r="J29" s="36"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1">
-      <c r="J30" s="33"/>
+      <c r="J30" s="36"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1">
-      <c r="J31" s="33"/>
+      <c r="J31" s="36"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1">
-      <c r="J32" s="33"/>
+      <c r="J32" s="36"/>
     </row>
     <row r="33" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J33" s="33"/>
+      <c r="J33" s="36"/>
     </row>
     <row r="34" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J34" s="33"/>
+      <c r="J34" s="36"/>
     </row>
     <row r="35" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J35" s="33"/>
+      <c r="J35" s="36"/>
     </row>
     <row r="36" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J36" s="33"/>
+      <c r="J36" s="36"/>
     </row>
     <row r="37" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J37" s="33"/>
+      <c r="J37" s="36"/>
     </row>
     <row r="38" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J38" s="33"/>
+      <c r="J38" s="36"/>
     </row>
     <row r="39" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J39" s="33"/>
+      <c r="J39" s="36"/>
     </row>
     <row r="40" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J40" s="33"/>
+      <c r="J40" s="36"/>
     </row>
     <row r="41" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J41" s="33"/>
+      <c r="J41" s="36"/>
     </row>
     <row r="42" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J42" s="33"/>
+      <c r="J42" s="36"/>
     </row>
     <row r="43" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J43" s="33"/>
+      <c r="J43" s="36"/>
     </row>
     <row r="44" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J44" s="33"/>
+      <c r="J44" s="36"/>
     </row>
     <row r="45" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J45" s="33"/>
+      <c r="J45" s="36"/>
     </row>
     <row r="46" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J46" s="33"/>
+      <c r="J46" s="36"/>
     </row>
     <row r="47" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J47" s="33"/>
+      <c r="J47" s="36"/>
     </row>
     <row r="48" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J48" s="33"/>
+      <c r="J48" s="36"/>
     </row>
     <row r="49" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J49" s="33"/>
+      <c r="J49" s="36"/>
     </row>
     <row r="50" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J50" s="33"/>
+      <c r="J50" s="36"/>
     </row>
     <row r="51" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J51" s="33"/>
+      <c r="J51" s="36"/>
     </row>
     <row r="52" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J52" s="33"/>
+      <c r="J52" s="36"/>
     </row>
     <row r="53" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J53" s="33"/>
+      <c r="J53" s="36"/>
     </row>
     <row r="54" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J54" s="33"/>
+      <c r="J54" s="36"/>
     </row>
     <row r="55" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J55" s="33"/>
+      <c r="J55" s="36"/>
     </row>
     <row r="56" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J56" s="33"/>
+      <c r="J56" s="36"/>
     </row>
     <row r="57" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J57" s="33"/>
+      <c r="J57" s="36"/>
     </row>
     <row r="58" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J58" s="33"/>
+      <c r="J58" s="36"/>
     </row>
     <row r="59" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J59" s="33"/>
+      <c r="J59" s="36"/>
     </row>
     <row r="60" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J60" s="33"/>
+      <c r="J60" s="36"/>
     </row>
     <row r="61" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J61" s="33"/>
+      <c r="J61" s="36"/>
     </row>
     <row r="62" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J62" s="33"/>
+      <c r="J62" s="36"/>
     </row>
     <row r="63" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J63" s="33"/>
+      <c r="J63" s="36"/>
     </row>
     <row r="64" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J64" s="33"/>
+      <c r="J64" s="36"/>
     </row>
     <row r="65" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J65" s="33"/>
+      <c r="J65" s="36"/>
     </row>
     <row r="66" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J66" s="33"/>
+      <c r="J66" s="36"/>
     </row>
     <row r="67" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J67" s="33"/>
+      <c r="J67" s="36"/>
     </row>
     <row r="68" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J68" s="33"/>
+      <c r="J68" s="36"/>
     </row>
     <row r="69" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J69" s="33"/>
+      <c r="J69" s="36"/>
     </row>
     <row r="70" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J70" s="33"/>
+      <c r="J70" s="36"/>
     </row>
     <row r="71" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J71" s="33"/>
+      <c r="J71" s="36"/>
     </row>
     <row r="72" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J72" s="33"/>
+      <c r="J72" s="36"/>
     </row>
     <row r="73" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J73" s="33"/>
+      <c r="J73" s="36"/>
     </row>
     <row r="74" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J74" s="33"/>
+      <c r="J74" s="36"/>
     </row>
     <row r="75" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J75" s="33"/>
+      <c r="J75" s="36"/>
     </row>
     <row r="76" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J76" s="33"/>
+      <c r="J76" s="36"/>
     </row>
     <row r="77" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J77" s="33"/>
+      <c r="J77" s="36"/>
     </row>
     <row r="78" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J78" s="33"/>
+      <c r="J78" s="36"/>
     </row>
     <row r="79" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J79" s="33"/>
+      <c r="J79" s="36"/>
     </row>
     <row r="80" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J80" s="33"/>
+      <c r="J80" s="36"/>
     </row>
     <row r="81" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J81" s="33"/>
+      <c r="J81" s="36"/>
     </row>
     <row r="82" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J82" s="33"/>
+      <c r="J82" s="36"/>
     </row>
     <row r="83" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J83" s="33"/>
+      <c r="J83" s="36"/>
     </row>
     <row r="84" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J84" s="33"/>
+      <c r="J84" s="36"/>
     </row>
     <row r="85" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J85" s="33"/>
+      <c r="J85" s="36"/>
     </row>
     <row r="86" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J86" s="33"/>
+      <c r="J86" s="36"/>
     </row>
     <row r="87" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J87" s="33"/>
+      <c r="J87" s="36"/>
     </row>
     <row r="88" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J88" s="33"/>
+      <c r="J88" s="36"/>
     </row>
     <row r="89" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J89" s="33"/>
+      <c r="J89" s="36"/>
     </row>
     <row r="90" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J90" s="33"/>
+      <c r="J90" s="36"/>
     </row>
     <row r="91" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J91" s="33"/>
+      <c r="J91" s="36"/>
     </row>
     <row r="92" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J92" s="33"/>
+      <c r="J92" s="36"/>
     </row>
     <row r="93" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J93" s="33"/>
+      <c r="J93" s="36"/>
     </row>
     <row r="94" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J94" s="33"/>
+      <c r="J94" s="36"/>
     </row>
     <row r="95" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J95" s="33"/>
+      <c r="J95" s="36"/>
     </row>
     <row r="96" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J96" s="33"/>
+      <c r="J96" s="36"/>
     </row>
     <row r="97" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J97" s="33"/>
+      <c r="J97" s="36"/>
     </row>
     <row r="98" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J98" s="33"/>
+      <c r="J98" s="36"/>
     </row>
     <row r="99" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J99" s="33"/>
+      <c r="J99" s="36"/>
     </row>
     <row r="100" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J100" s="33"/>
+      <c r="J100" s="36"/>
     </row>
     <row r="101" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J101" s="33"/>
+      <c r="J101" s="36"/>
     </row>
     <row r="102" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J102" s="33"/>
+      <c r="J102" s="36"/>
     </row>
     <row r="103" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J103" s="33"/>
+      <c r="J103" s="36"/>
     </row>
     <row r="104" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J104" s="33"/>
+      <c r="J104" s="36"/>
     </row>
     <row r="105" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J105" s="33"/>
+      <c r="J105" s="36"/>
     </row>
     <row r="106" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J106" s="33"/>
+      <c r="J106" s="36"/>
     </row>
     <row r="107" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J107" s="33"/>
+      <c r="J107" s="36"/>
     </row>
     <row r="108" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J108" s="33"/>
+      <c r="J108" s="36"/>
     </row>
     <row r="109" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J109" s="33"/>
+      <c r="J109" s="36"/>
     </row>
     <row r="110" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J110" s="33"/>
+      <c r="J110" s="36"/>
     </row>
     <row r="111" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J111" s="33"/>
+      <c r="J111" s="36"/>
     </row>
     <row r="112" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J112" s="33"/>
+      <c r="J112" s="36"/>
     </row>
     <row r="113" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J113" s="33"/>
+      <c r="J113" s="36"/>
     </row>
     <row r="114" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J114" s="33"/>
+      <c r="J114" s="36"/>
     </row>
     <row r="115" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J115" s="33"/>
+      <c r="J115" s="36"/>
     </row>
     <row r="116" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J116" s="33"/>
+      <c r="J116" s="36"/>
     </row>
     <row r="117" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J117" s="33"/>
+      <c r="J117" s="36"/>
     </row>
     <row r="118" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J118" s="33"/>
+      <c r="J118" s="36"/>
     </row>
     <row r="119" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J119" s="33"/>
+      <c r="J119" s="36"/>
     </row>
     <row r="120" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J120" s="33"/>
+      <c r="J120" s="36"/>
     </row>
     <row r="121" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J121" s="33"/>
+      <c r="J121" s="36"/>
     </row>
     <row r="122" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J122" s="33"/>
+      <c r="J122" s="36"/>
     </row>
     <row r="123" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J123" s="33"/>
+      <c r="J123" s="36"/>
     </row>
     <row r="124" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J124" s="33"/>
+      <c r="J124" s="36"/>
     </row>
     <row r="125" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J125" s="33"/>
+      <c r="J125" s="36"/>
     </row>
     <row r="126" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J126" s="33"/>
+      <c r="J126" s="36"/>
     </row>
     <row r="127" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J127" s="33"/>
+      <c r="J127" s="36"/>
     </row>
     <row r="128" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J128" s="33"/>
+      <c r="J128" s="36"/>
     </row>
     <row r="129" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J129" s="33"/>
+      <c r="J129" s="36"/>
     </row>
     <row r="130" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J130" s="33"/>
+      <c r="J130" s="36"/>
     </row>
     <row r="131" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J131" s="33"/>
+      <c r="J131" s="36"/>
     </row>
     <row r="132" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J132" s="33"/>
+      <c r="J132" s="36"/>
     </row>
     <row r="133" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J133" s="33"/>
+      <c r="J133" s="36"/>
     </row>
     <row r="134" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J134" s="33"/>
+      <c r="J134" s="36"/>
     </row>
     <row r="135" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J135" s="33"/>
+      <c r="J135" s="36"/>
     </row>
     <row r="136" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J136" s="33"/>
+      <c r="J136" s="36"/>
     </row>
     <row r="137" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J137" s="33"/>
+      <c r="J137" s="36"/>
     </row>
     <row r="138" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J138" s="33"/>
+      <c r="J138" s="36"/>
     </row>
     <row r="139" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J139" s="33"/>
+      <c r="J139" s="36"/>
     </row>
     <row r="140" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J140" s="33"/>
+      <c r="J140" s="36"/>
     </row>
     <row r="141" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J141" s="33"/>
+      <c r="J141" s="36"/>
     </row>
     <row r="142" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J142" s="33"/>
+      <c r="J142" s="36"/>
     </row>
     <row r="143" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J143" s="33"/>
+      <c r="J143" s="36"/>
     </row>
     <row r="144" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J144" s="33"/>
+      <c r="J144" s="36"/>
     </row>
     <row r="145" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J145" s="33"/>
+      <c r="J145" s="36"/>
     </row>
     <row r="146" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J146" s="33"/>
+      <c r="J146" s="36"/>
     </row>
     <row r="147" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J147" s="33"/>
+      <c r="J147" s="36"/>
     </row>
     <row r="148" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J148" s="33"/>
+      <c r="J148" s="36"/>
     </row>
     <row r="149" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J149" s="33"/>
+      <c r="J149" s="36"/>
     </row>
     <row r="150" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J150" s="33"/>
+      <c r="J150" s="36"/>
     </row>
     <row r="151" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J151" s="33"/>
+      <c r="J151" s="36"/>
     </row>
     <row r="152" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J152" s="33"/>
+      <c r="J152" s="36"/>
     </row>
     <row r="153" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J153" s="33"/>
+      <c r="J153" s="36"/>
     </row>
     <row r="154" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J154" s="33"/>
+      <c r="J154" s="36"/>
     </row>
     <row r="155" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J155" s="33"/>
+      <c r="J155" s="36"/>
     </row>
     <row r="156" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J156" s="33"/>
+      <c r="J156" s="36"/>
     </row>
     <row r="157" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J157" s="33"/>
+      <c r="J157" s="36"/>
     </row>
     <row r="158" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J158" s="33"/>
+      <c r="J158" s="36"/>
     </row>
     <row r="159" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J159" s="33"/>
+      <c r="J159" s="36"/>
     </row>
     <row r="160" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J160" s="33"/>
+      <c r="J160" s="36"/>
     </row>
     <row r="161" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J161" s="33"/>
+      <c r="J161" s="36"/>
     </row>
     <row r="162" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J162" s="33"/>
+      <c r="J162" s="36"/>
     </row>
     <row r="163" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J163" s="33"/>
+      <c r="J163" s="36"/>
     </row>
     <row r="164" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J164" s="33"/>
+      <c r="J164" s="36"/>
     </row>
     <row r="165" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J165" s="33"/>
+      <c r="J165" s="36"/>
     </row>
     <row r="166" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J166" s="33"/>
+      <c r="J166" s="36"/>
     </row>
     <row r="167" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J167" s="33"/>
+      <c r="J167" s="36"/>
     </row>
     <row r="168" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J168" s="33"/>
+      <c r="J168" s="36"/>
     </row>
     <row r="169" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J169" s="33"/>
+      <c r="J169" s="36"/>
     </row>
     <row r="170" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J170" s="33"/>
+      <c r="J170" s="36"/>
     </row>
     <row r="171" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J171" s="33"/>
+      <c r="J171" s="36"/>
     </row>
     <row r="172" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J172" s="33"/>
+      <c r="J172" s="36"/>
     </row>
     <row r="173" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J173" s="33"/>
+      <c r="J173" s="36"/>
     </row>
     <row r="174" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J174" s="33"/>
+      <c r="J174" s="36"/>
     </row>
     <row r="175" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J175" s="33"/>
+      <c r="J175" s="36"/>
     </row>
     <row r="176" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J176" s="33"/>
+      <c r="J176" s="36"/>
     </row>
     <row r="177" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J177" s="33"/>
+      <c r="J177" s="36"/>
     </row>
     <row r="178" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J178" s="33"/>
+      <c r="J178" s="36"/>
     </row>
     <row r="179" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J179" s="33"/>
+      <c r="J179" s="36"/>
     </row>
     <row r="180" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J180" s="33"/>
+      <c r="J180" s="36"/>
     </row>
     <row r="181" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J181" s="33"/>
+      <c r="J181" s="36"/>
     </row>
     <row r="182" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J182" s="33"/>
+      <c r="J182" s="36"/>
     </row>
     <row r="183" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J183" s="33"/>
+      <c r="J183" s="36"/>
     </row>
     <row r="184" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J184" s="33"/>
+      <c r="J184" s="36"/>
     </row>
     <row r="185" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J185" s="33"/>
+      <c r="J185" s="36"/>
     </row>
     <row r="186" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J186" s="33"/>
+      <c r="J186" s="36"/>
     </row>
     <row r="187" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J187" s="33"/>
+      <c r="J187" s="36"/>
     </row>
     <row r="188" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J188" s="33"/>
+      <c r="J188" s="36"/>
     </row>
     <row r="189" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J189" s="33"/>
+      <c r="J189" s="36"/>
     </row>
     <row r="190" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J190" s="33"/>
+      <c r="J190" s="36"/>
     </row>
     <row r="191" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J191" s="33"/>
+      <c r="J191" s="36"/>
     </row>
     <row r="192" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J192" s="33"/>
+      <c r="J192" s="36"/>
     </row>
     <row r="193" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J193" s="33"/>
+      <c r="J193" s="36"/>
     </row>
     <row r="194" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J194" s="33"/>
+      <c r="J194" s="36"/>
     </row>
     <row r="195" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J195" s="33"/>
+      <c r="J195" s="36"/>
     </row>
     <row r="196" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J196" s="33"/>
+      <c r="J196" s="36"/>
     </row>
     <row r="197" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J197" s="33"/>
+      <c r="J197" s="36"/>
     </row>
     <row r="198" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J198" s="33"/>
+      <c r="J198" s="36"/>
     </row>
     <row r="199" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J199" s="33"/>
+      <c r="J199" s="36"/>
     </row>
     <row r="200" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J200" s="33"/>
+      <c r="J200" s="36"/>
     </row>
     <row r="201" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J201" s="33"/>
+      <c r="J201" s="36"/>
     </row>
     <row r="202" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J202" s="33"/>
+      <c r="J202" s="36"/>
     </row>
     <row r="203" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J203" s="33"/>
+      <c r="J203" s="36"/>
     </row>
     <row r="204" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J204" s="33"/>
+      <c r="J204" s="36"/>
     </row>
     <row r="205" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J205" s="33"/>
+      <c r="J205" s="36"/>
     </row>
     <row r="206" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J206" s="33"/>
+      <c r="J206" s="36"/>
     </row>
     <row r="207" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J207" s="33"/>
+      <c r="J207" s="36"/>
     </row>
     <row r="208" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J208" s="33"/>
+      <c r="J208" s="36"/>
     </row>
     <row r="209" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J209" s="33"/>
+      <c r="J209" s="36"/>
     </row>
     <row r="210" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J210" s="33"/>
+      <c r="J210" s="36"/>
     </row>
     <row r="211" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J211" s="33"/>
+      <c r="J211" s="36"/>
     </row>
     <row r="212" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J212" s="33"/>
+      <c r="J212" s="36"/>
     </row>
     <row r="213" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J213" s="33"/>
+      <c r="J213" s="36"/>
     </row>
     <row r="214" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J214" s="33"/>
+      <c r="J214" s="36"/>
     </row>
     <row r="215" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J215" s="33"/>
+      <c r="J215" s="36"/>
     </row>
     <row r="216" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J216" s="33"/>
+      <c r="J216" s="36"/>
     </row>
     <row r="217" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J217" s="33"/>
+      <c r="J217" s="36"/>
     </row>
     <row r="218" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J218" s="33"/>
+      <c r="J218" s="36"/>
     </row>
     <row r="219" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J219" s="33"/>
+      <c r="J219" s="36"/>
     </row>
     <row r="220" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J220" s="33"/>
+      <c r="J220" s="36"/>
     </row>
     <row r="221" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J221" s="33"/>
+      <c r="J221" s="36"/>
     </row>
     <row r="222" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J222" s="33"/>
+      <c r="J222" s="36"/>
     </row>
     <row r="223" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J223" s="33"/>
+      <c r="J223" s="36"/>
     </row>
     <row r="224" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J224" s="33"/>
+      <c r="J224" s="36"/>
     </row>
     <row r="225" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J225" s="33"/>
+      <c r="J225" s="36"/>
     </row>
     <row r="226" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J226" s="33"/>
+      <c r="J226" s="36"/>
     </row>
     <row r="227" spans="10:10" ht="15.75" customHeight="1">
-      <c r="J227" s="33"/>
+      <c r="J227" s="36"/>
     </row>
     <row r="228" spans="10:10" ht="15.75" customHeight="1"/>
     <row r="229" spans="10:10" ht="15.75" customHeight="1"/>
@@ -10903,59 +10697,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A1" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="B1" s="12" t="s">
+      <c r="A1" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A2" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="B2" s="39" t="s">
-        <v>215</v>
+      <c r="A2" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="126">
-      <c r="A3" s="34" t="s">
-        <v>201</v>
-      </c>
-      <c r="B3" s="35" t="s">
-        <v>202</v>
+      <c r="A3" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="84">
-      <c r="A4" s="34" t="s">
-        <v>203</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>204</v>
+      <c r="A4" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="105">
-      <c r="A5" s="34" t="s">
-        <v>205</v>
-      </c>
-      <c r="B5" s="35" t="s">
-        <v>206</v>
+      <c r="A5" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="105">
-      <c r="A6" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>208</v>
+      <c r="A6" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="105">
-      <c r="A7" s="34" t="s">
-        <v>209</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>210</v>
+      <c r="A7" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75" customHeight="1"/>
@@ -11963,33 +11757,33 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="24.5" style="37" customWidth="1"/>
-    <col min="2" max="2" width="27.1640625" style="37" customWidth="1"/>
-    <col min="3" max="16384" width="11" style="37"/>
+    <col min="1" max="1" width="24.5" style="16" customWidth="1"/>
+    <col min="2" max="2" width="27.1640625" style="16" customWidth="1"/>
+    <col min="3" max="16384" width="11" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="B1" s="37" t="s">
+      <c r="A1" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="B2" s="37" t="s">
-        <v>213</v>
+      <c r="A2" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="37" t="s">
-        <v>211</v>
-      </c>
-      <c r="B3" s="40" t="s">
-        <v>216</v>
+      <c r="A3" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>
